--- a/Asset-Mapping.xlsx
+++ b/Asset-Mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifmworld-my.sharepoint.com/personal/nathalie_nuber_ifm_com/Documents/Documents/DHBW/Bachelorarbeit/Bachelorarbeit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="438" documentId="8_{7646D5EB-5A7E-4C2C-B298-2CCD9ED2279B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FE8BC06-7E67-4ADA-A37B-53CF4D30CFE2}"/>
+  <xr:revisionPtr revIDLastSave="571" documentId="8_{7646D5EB-5A7E-4C2C-B298-2CCD9ED2279B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F21E7CA3-590C-4821-AEEF-968A2E3949A0}"/>
   <bookViews>
-    <workbookView xWindow="28635" yWindow="-165" windowWidth="29130" windowHeight="15810" xr2:uid="{4A49BA81-CDEC-4679-BB9D-EFEA5E788525}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A49BA81-CDEC-4679-BB9D-EFEA5E788525}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="169">
   <si>
     <t>MVO-ID</t>
   </si>
@@ -374,24 +374,11 @@
     <t>Das COM-Modul verarbeitet PROFINET, während PROFIsafe als „Black Channel" durch die nicht-sichere Kommunikation getunnelt wird – die PROFIsafe-Frames werden dabei per CRC/Watchdog-Mechanismus auf Integrität geprüft. --&gt; Protokollvalidierung prüft nur Daten die bereits am Gerät angekommen sind</t>
   </si>
   <si>
-    <t>Protocoll-Validation through PROFINET/PROFIsafe-Stack +
-Network Isolation (safe zone behind a firewall)</t>
-  </si>
-  <si>
     <t>PRROFIsafe Black-Channel principle &amp; 4-Byte-CRC (F_iParCRC, F_ParCRC)+
 physical manipulation security of the rotary switches thorugh plastic/metal seals</t>
   </si>
   <si>
-    <t>EDR 3.1  RE(1) nicht belegt</t>
-  </si>
-  <si>
     <t>Gap (only physical seal + visuell inspection, but no automatic hardware logging)</t>
-  </si>
-  <si>
-    <t>Nmap</t>
-  </si>
-  <si>
-    <t>keine kryptographische Signatur oder einen Integritätsschutz für die swrevision/hwversion-Felder</t>
   </si>
   <si>
     <t xml:space="preserve"> Version-Identification-API via IoT-Core (`/deviceinfo/hwversion`, `/deviceinfo/swrevision`, `/deviceinfo/swinfo/scpuversion`).
@@ -415,7 +402,260 @@
 `/scpubootloaderversion`</t>
   </si>
   <si>
-    <t>Api-Availability (max 2 aktive HTTP-Connections) with exception: Access during Update</t>
+    <t>Intervention Audit Logging (Config-Changes over REVISION_COUNTER)+ 
+Physical Deactivation instead of logging (Test-/Debug-Interface)</t>
+  </si>
+  <si>
+    <t>REVISION_COUNTER + iParCRC-Comparison ​​+
+FW/HW-Compatibility-Check per Component and Release Notes​​</t>
+  </si>
+  <si>
+    <t>External Hardware Watchdog +
+Controlled Fallback in Failsafe-State (State Machine)​​
+HTTP-Connection-Limit (max. 2)​​</t>
+  </si>
+  <si>
+    <t>Physical Access Control via Rotary/DIL-Switch &amp; Power-Cycle +
+externally delegated Configuration Authorization (PLC/CRC-Tool)​</t>
+  </si>
+  <si>
+    <t>Non-volatile circular buffer log (≥100 entries, survives non-cold-start resets) 
+with conflict “5-year” requirement</t>
+  </si>
+  <si>
+    <t>External Release Notes (Website) +
+Current version display via IoT Core​​</t>
+  </si>
+  <si>
+    <t>Api-Availability (max 2 aktive HTTP-Connections) with exception: 
+Access during Update</t>
+  </si>
+  <si>
+    <t>No delete command documented over the network + 
+No read protection, no purpose limitation</t>
+  </si>
+  <si>
+    <t>Test Tool= 
+Standardwerkzeug passend zum Zugriffstyp​ ​
+gefiltert durch Frage: 
+Existenz der Angriffsfläche  &amp; 
+Komponenteneigenschaft&amp; 
+präzises Erfolgskriterium​​
+D</t>
+  </si>
+  <si>
+    <t>Nmap (Network Discovery/Port Scanning) + Network/Protocol Fuzzer (boofuzz, Mutiny) für den [K]-Teil (Protokoll-Validierung); Netzwerkisolation ([A]-Teil) nicht per Tool testbar, nur Ruleset/System Configuration Review (Dokumentenprüfung Firewall-Topologie)</t>
+  </si>
+  <si>
+    <t>Network/Protocol Fuzzer (boofuzz/Mutiny, um CRC-Verletzung im PROFIsafe-Frame zu provozieren); für den physischen Teil kein automatisiertes Tool – manuelle Physical-Access-Prüfung gemäß ISTG-Zugriffsmodell (PA-4, invasive physical access)</t>
+  </si>
+  <si>
+    <t>Log Review (NIST-Technik zur Prüfung, ob Ereignisdaten überhaupt erzeugt werden) + manuelle Siegel-/Sichtprüfung; nicht anwendbar, da laut Dokumentation kein automatisiertes Hardware-Event-Log existiert, gegen das getestet werden könnte</t>
+  </si>
+  <si>
+    <t>curl, OWASP ZAP (Embedded Web Application Testing, explizit für unauthentifizierte Informationsabfrage)</t>
+  </si>
+  <si>
+    <t>curl (Upload manipulierter Firmware) + binwalk (Stage 3: Analyzing Firmware – zur Strukturanalyse des Update-Containers und Auffinden der CRC-Header); PASS-Kriterium: Ablehnung bei CRC-Mismatch im Update Container Header</t>
+  </si>
+  <si>
+    <t>curl, OWASP ZAP (Verifikation des Read-Only-Zugriffs auf I&amp;M4)</t>
+  </si>
+  <si>
+    <t>NCrack/Lastgenerierung gegen das Connection-Limit (NIST BackTrack-Toolkit-Referenz für Vulnerability-Scanning-Kategorie) + manueller Funktionstest der Erreichbarkeit während des State „Update"</t>
+  </si>
+  <si>
+    <t>Nmap/NCrack für Lasttest gegen HTTP-Limit; für Watchdog/Fallback: Network/Protocol Fuzzer zur gezielten Störung der PROFINET-Kommunikation, um Failsafe-Übergang zu verifizieren</t>
+  </si>
+  <si>
+    <t>curl/OWASP ZAP (Unauth GET Request auf /devicestatus/errorlog/loglist, Embedded Web Application Testing)</t>
+  </si>
+  <si>
+    <t>Log Review (NIST-Technik) + curl für wiederholte Update-Zyklen, um zu prüfen, ob eine geräteseitige Mehrfach-Update-Historie existiert</t>
+  </si>
+  <si>
+    <t>Log Review (NIST-Technik zur Prüfung von Zeitstempeln, Buffer-Wraparound, sowie gezielter Vergleich Coldstart- vs. Nicht-Coldstart-Reset)</t>
+  </si>
+  <si>
+    <t>stattdessen OWASP ZAP (Verifikation Read-Only-Enforcement der IoT-Core-API) + manueller Schreibversuch ohne korrekte Rotary-Switch-Stellung, gemäß ISTG-Authorization-Testmethodik (Unauthorized-Access-Test)</t>
+  </si>
+  <si>
+    <t>curl (Update triggern) + Log Review (Versionshistorie/Revision-Counter-Prüfung)</t>
+  </si>
+  <si>
+    <t>OWASP ZAP (Event triggern über IoT-Core) + Log Review (NIST-Technik); für das Debug-Interface: JTAGulator/UART-Tools (minicom, picocom) nur relevant, falls Interface nicht vollständig gefused ist</t>
+  </si>
+  <si>
+    <t>SVV-3 Vulnerability Testing</t>
+  </si>
+  <si>
+    <t>SVV-1 + SVV2</t>
+  </si>
+  <si>
+    <t>SVV1+ SVV3</t>
+  </si>
+  <si>
+    <t>SVV2 + SVV4</t>
+  </si>
+  <si>
+    <t>SVV3</t>
+  </si>
+  <si>
+    <t>SVV4 Penetration Testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SVV4 </t>
+  </si>
+  <si>
+    <t>SVV1</t>
+  </si>
+  <si>
+    <t>ISTG-DES-AUTHZ-001, ISTG-DES-INFO-001/002</t>
+  </si>
+  <si>
+    <t>ISTG-DES-CRYPT-001, ISTG-DES-LOGIC-001</t>
+  </si>
+  <si>
+    <t>ISTG-UI-AUTHZ-001/002, ISTG-UI-INPV-001/002</t>
+  </si>
+  <si>
+    <t>ISTG-FW[UPDT]-CRYPT-001…004, ISTG-FW[UPDT]-LOGIC-001 (Rollback)</t>
+  </si>
+  <si>
+    <t>ISTG-FW[INST]-AUTHZ-001/002, ISTG-FW[INST]-CRYPT-001 (Bootloader-Signatur)</t>
+  </si>
+  <si>
+    <t>ISTG-INT-AUTHZ-001, ISTG-PROC-AUTHZ-001</t>
+  </si>
+  <si>
+    <t>ISTG-INT[UART]-AUTHZ-001/002, ISTG-INT[UART]-INFO-001/002, ISTG-INT[UART]-INPV-001</t>
+  </si>
+  <si>
+    <t>ISTG-INT[I2C]-AUTHZ-001, -INFO-001/002/003, -INPV-001</t>
+  </si>
+  <si>
+    <t>ISTG-PHY-AUTHZ-001, ISTG-PHY-LOGIC-001</t>
+  </si>
+  <si>
+    <t>ISTG-MEM-INFO-001…005, ISTG-MEM-SCRT-001, ISTG-MEM-CRYPT-001</t>
+  </si>
+  <si>
+    <t>ISTG-DES-LOGIC-001, ISTG-DES-INPV-001/002</t>
+  </si>
+  <si>
+    <t>ISTG-*-CRYPT-001 (Kategorie-übergreifend), ASVS V11 Cryptography</t>
+  </si>
+  <si>
+    <t>ISTG-FW-CONF-001/002, ISTG-DES-CONF-001/002</t>
+  </si>
+  <si>
+    <t>– (NIST-Technik, nicht ISTG-spezifisch)</t>
+  </si>
+  <si>
+    <t>Wireshark (mit PROFINET/PROFIsafe-Dissector), Scapy (Custom PROFINET-Layer für Paket-Manipulation), 
+Nmap (Segmentierungs-/Firewall-Verifikation), 
+Ettercap/arpspoof (Spoofing-Simulation)</t>
+  </si>
+  <si>
+    <t>Scapy-Skript zur gezielten CRC-Korruption (F_iParCRC/F_ParCRC), 
+Wireshark (PROFIsafe-Telegramm-Analyse), 
+physisch: Drehmoment-Werkzeug, Lupe/UV-Lampe zur Siegel-Inspektion, 
+Kamera zur Beweisdokumentation</t>
+  </si>
+  <si>
+    <t>Kein Software-Tool – manuelle physische Manipulation + Fotodokumentation + 
+Checkliste (da Lücke: keine automatische HW-Loggingfunktion vorhanden)</t>
+  </si>
+  <si>
+    <t>curl/Postman, OWASP ZAP oder Burp Suite (Interception), 
+Wireshark (Klartext-HTTP-Erfassung), 
+Nmap (Service-Discovery)</t>
+  </si>
+  <si>
+    <t>binwalk (Firmware-Image-Analyse), 
+Hex-Editor, eigenes Python-Skript zur CRC-Neuberechnung nach Manipulation, 
+Update-Workflow über Engineering-Tool (z. B. TIA Portal/CRC-Tool)</t>
+  </si>
+  <si>
+    <t>curl/Postman, OWASP ZAP, Nmap</t>
+  </si>
+  <si>
+    <t>Apache JMeter oder hping3, 
+eigenes Python-Skript (asyncio/requests für &gt;2 gleichzeitige Verbindungen), 
+Slowloris-Variante</t>
+  </si>
+  <si>
+    <t>Config-Änderung via Engineering-Tool (TIA Portal/CRC-Tool), 
+Log-Readout via ZAP/curl, 
+physisch: JTAGulator, 
+Bus Pirate, Logic Analyzer am Test-/Debug-Pin</t>
+  </si>
+  <si>
+    <t>Wie RQ-008, zusätzlich gezielter FW/HW-Mismatch-Test über Update-Tool, 
+Skript zum Abgleich REVISION_COUNTER/iParCRC via API</t>
+  </si>
+  <si>
+    <t>hping3/Scapy (Netzwerkflutung), 
+Ostinato (Traffic-Generator), 
+Oszilloskop/Multimeter am Watchdog-Signal, 
+kombiniert mit HTTP-Flood aus RQ-007</t>
+  </si>
+  <si>
+    <t>Physischer Bypass-Versuch (Schalterstellung ohne Power-Cycle-Prozedur), 
+Engineering-Tool für Autorisierungs-Bypass-Test, 
+Postman/ZAP für direkten API-Schreibzugriff unter Umgehung der PLC-Delegation</t>
+  </si>
+  <si>
+    <t>Eigenes Python-Skript zur automatisierten Erzeugung von &gt;100 Interventionen, 
+wiederholte Power-Cycle-Tests (Non-Cold-Start), 
+Log-Readout via API</t>
+  </si>
+  <si>
+    <t>curl/ZAP (Versionsabfrage via IoT-Core), 
+manueller Abgleich mit Release-Notes-Website</t>
+  </si>
+  <si>
+    <t>OWASP ZAP/Burp Suite (Active Scan), 
+ffuf/wfuzz (Endpoint-Fuzzing nach undokumentierten Delete-Befehlen), 
+Wireshark (Prüfung auf fehlenden Transportschutz)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Protocoll-Validation through PROFINET/PROFIsafe-Stack </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(H)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">+
+Network Isolation (safe zone behind a firewall) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(F)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -473,15 +713,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" textRotation="180" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -489,9 +729,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -508,6 +745,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -827,17 +1068,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB352A9E-FA09-4936-805B-24B06A598CDB}">
-  <dimension ref="A3:N60"/>
+  <dimension ref="A3:P60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="11.42578125" style="1"/>
     <col min="3" max="4" width="29.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="25.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="67.5703125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.42578125" style="1"/>
+    <col min="7" max="7" width="43.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="42.85546875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
@@ -853,18 +1096,15 @@
       <c r="F3" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
+      <c r="L3" s="4" t="s">
+        <v>106</v>
+      </c>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
-    </row>
-    <row r="4" spans="2:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+    </row>
+    <row r="4" spans="2:16" ht="90" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
@@ -878,13 +1118,22 @@
         <v>89</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>101</v>
+        <v>168</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" ht="60" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" ht="90" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
@@ -898,13 +1147,22 @@
         <v>90</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" ht="60" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -918,10 +1176,22 @@
         <v>91</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" ht="60" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" ht="60" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
@@ -935,13 +1205,22 @@
         <v>92</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" ht="75" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
@@ -955,13 +1234,22 @@
         <v>90</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" ht="60" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" ht="60" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
@@ -975,10 +1263,22 @@
         <v>90</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" ht="60" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
@@ -991,11 +1291,23 @@
       <c r="E10" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="F10" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" ht="75" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
@@ -1008,8 +1320,23 @@
       <c r="E11" s="1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="12" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="F11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="60" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
@@ -1022,8 +1349,23 @@
       <c r="E12" s="1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="13" spans="2:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
@@ -1036,8 +1378,23 @@
       <c r="E13" s="1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="14" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="F13" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" ht="90" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
@@ -1050,8 +1407,23 @@
       <c r="E14" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="F14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="75" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
@@ -1064,8 +1436,23 @@
       <c r="E15" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="F15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" ht="45" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>13</v>
       </c>
@@ -1078,8 +1465,23 @@
       <c r="E16" s="1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="69" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>14</v>
       </c>
@@ -1092,16 +1494,34 @@
       <c r="E17" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="95.25" x14ac:dyDescent="0.25">
+      <c r="F17" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="258" x14ac:dyDescent="0.25">
       <c r="E19" s="3" t="s">
         <v>96</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>27</v>
       </c>
@@ -1109,7 +1529,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>28</v>
       </c>
@@ -1117,7 +1537,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>29</v>
       </c>
@@ -1125,7 +1545,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>30</v>
       </c>
@@ -1133,7 +1553,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>86</v>
       </c>
@@ -1144,7 +1564,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>32</v>
       </c>
@@ -1152,7 +1572,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>33</v>
       </c>
@@ -1160,7 +1580,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>34</v>
       </c>
@@ -1168,7 +1588,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
         <v>66</v>
       </c>
@@ -1309,7 +1729,7 @@
         <v>5</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -1317,7 +1737,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Asset-Mapping.xlsx
+++ b/Asset-Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifmworld-my.sharepoint.com/personal/nathalie_nuber_ifm_com/Documents/Documents/DHBW/Bachelorarbeit/Bachelorarbeit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="967" documentId="8_{7646D5EB-5A7E-4C2C-B298-2CCD9ED2279B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{485D708D-D8C4-463F-BC73-0E53B02BF017}"/>
+  <xr:revisionPtr revIDLastSave="1177" documentId="8_{7646D5EB-5A7E-4C2C-B298-2CCD9ED2279B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A6B79AE-5AF1-4863-89D9-F98107862183}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A49BA81-CDEC-4679-BB9D-EFEA5E788525}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="246">
   <si>
     <t>MVO-ID</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>CR 7.8</t>
-  </si>
-  <si>
-    <t>CR 3.4, EDR 3.14</t>
   </si>
   <si>
     <t>CR 2.8, CR 2.12, CR 3.4</t>
@@ -211,10 +208,6 @@
     <t>Eingebettete Geräte müssen die Integrität der für den Boot-Prozess benötigten Firmware, Software und Konfigurationsdaten vor deren Anwendung beim Booten verifizieren.</t>
   </si>
   <si>
-    <t>B (Config), 
-D (Update Workflow)</t>
-  </si>
-  <si>
     <t>D (Safety Firmware)</t>
   </si>
   <si>
@@ -280,24 +273,6 @@
   </si>
   <si>
     <t>Threat (STRIDE)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">A (Trusted Safety Function),
-H (Network),
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(E Safety Monitoring)</t>
-    </r>
   </si>
   <si>
     <t>Spoofing
@@ -356,11 +331,6 @@
     <t>Gap</t>
   </si>
   <si>
-    <t>Freedom from hazard on the non-safety COM/IoT path relies on the assumption 
-``used in a safe zone behind a firewall'' (SRIO-9402) 
---&gt; not verifiable by functional testing of the device alone</t>
-  </si>
-  <si>
     <t>C (Process Data),
 G (Rotary Switches- OP-Mode)</t>
   </si>
@@ -394,68 +364,12 @@
 and process parameters, checked by SCPU each parametrization cycle.</t>
   </si>
   <si>
-    <t>CRC-based check only ;
-no cryptographic signature/HMAC verification (SRSL3-equivalent per prEN 50742 \S7.4.3.4.1 not reached); 
-reliable only against accidental corruption, not deliberate tampering.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Tampering
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Information Disclosure</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Identification data is transmitted only via unencrypted HTTP (HTTPS/Websocket/MQTT explicitly unsupported);
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>secondary Information Disclosure risk on the physical Ethernet interface (reconnaissance of exact FW/HW versions)</t>
-    </r>
-  </si>
-  <si>
     <t>Software inventory read-out via IoT-Core 
 (/deviceinfo/swinfo/cpubootloaderversion, /scpuversion, /scpubootloaderversion).</t>
   </si>
   <si>
     <t>Identification data is transmitted only via unencrypted HTTP 
 (HTTPS/Websocket/MQTT explicitly unsupported)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">H (Availability); 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">D (identification data) </t>
-    </r>
   </si>
   <si>
     <t>Max. 2 concurrent HTTP connections limit resource exhaustion of the IoT-Core service.</t>
@@ -476,67 +390,12 @@
 I (Audit Data)</t>
   </si>
   <si>
-    <t>REVISION\_COUNTER + iParCRC comparison on configuration change; 
-FW/HW compatibility check per component plus Release Notes on firmware change.</t>
-  </si>
-  <si>
-    <t>REVISION\_COUNTER records that a change occurred, but not who performed it or when;
-no timestamp/actor field documented, limiting genuine non-repudiation value.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">External hardware watchdog and PROFIsafe F\_WD\_Time device-acknowledgment watchdog trigger a controlled fallback to a defined failsafe state on communication loss (state transition 9); 
-max. 2 concurrent HTTP connections limit COM/IoT-side resource exhaustion. </t>
-  </si>
-  <si>
     <t>Mitigations address loss/staleness of communication, not a deliberate flooding/DoS attack on the PROFINET stack itself ;
 no rate-limiting or flood-protection (cf. CR 7.1 RE(1)) documented for the fieldbus interface.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Tampering, 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Spoofing, 
-Elevation of Privilege</t>
-    </r>
-  </si>
-  <si>
     <t>F-Address change and FW-Update mode entry require physical access to the rotary/DIL switches plus a power-cycle;
 a physical-presence barrier for these two specific actions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Major finding: password protection for safety-parameter writes was explicitly dropped ; 
-IoT-Core was made read-only instead. 
-Parameter writes are only possible via the fieldbus/PLC engineering tool; 
-authorization is fully delegated to an external, unverified assumption (locked control cabinet, restricted network access). 
-CR 1.1/1.2/2.1 are therefore not enforced on the device itself. 
-Additionally, no mechanism exists for learning-phase settings </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I (Audit Data); 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">B, D, G (logged sources) </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Non-volatile circular buffer log (≥100 entries, survives non-cold-start resets) </t>
@@ -724,18 +583,6 @@
     </r>
   </si>
   <si>
-    <t>\Cite{10275637}</t>
-  </si>
-  <si>
-    <t>REVISION\_COUNTER increment (I\&amp;M0data) on every parameter change 
-provides a basic non-repudiation marker for configuration interventions.</t>
-  </si>
-  <si>
-    <t>B (Config); D (Safety Firmware)
-G (Operating Mode); 
-I (Audit Data)</t>
-  </si>
-  <si>
     <t>Network (PROFINET acyclic/I&amp;M0 records);
 Physical (Debug interface)</t>
   </si>
@@ -758,10 +605,6 @@
 Network Sniffing / Protocol Analysis</t>
   </si>
   <si>
-    <t>Protocol Integrity &amp; Fuzzing (Fieldbus-specific); 
-Physical Interface Testing (Tamper)</t>
-  </si>
-  <si>
     <t>Physical Interface Testing / Hardware Debug Access;
 Log/Audit Review</t>
   </si>
@@ -770,9 +613,6 @@
 Network Sniffing (Cleartext-Traffic)</t>
   </si>
   <si>
-    <t>Protocol Integrity &amp; Fuzzing (Fieldbus-specific)</t>
-  </si>
-  <si>
     <t>Web Application Analysis (Information Disclosure)</t>
   </si>
   <si>
@@ -807,61 +647,13 @@
 Information Disclosure Testing</t>
   </si>
   <si>
-    <t>Prüft, ob nicht vorgesehene Dienste/Ports auf dem Non-Safety-COM-Pfad erreichbar sind; 
-Wireshark verifiziert F_Dest_Add/F_Source_Add-Handling</t>
-  </si>
-  <si>
-    <t>Scapy (Python, custom PROFINET-Frame-Manipulation) oder 
-boofuzz (PROFIsafe-Modul) 
-+ physische Siegelprüfung (manuell)</t>
-  </si>
-  <si>
-    <t>CRC-Kollisionsangriff erfordert gezielte Paket-Manipulation, 
-kein Standard-Scanner deckt PROFIsafe-CRC ab</t>
-  </si>
-  <si>
-    <t>JTAGulator / Logic-Analyzer (sigrok/PulseView) 
-+ manuelle Inspektion</t>
-  </si>
-  <si>
-    <t>Identifiziert Debug-Pads/Interfaces am Gehäuse; 
-da "SVV-1 negative confirmation" reicht hier Dokumentenprüfung 
-+ physischer Zugriffstest</t>
-  </si>
-  <si>
-    <t>Nikto/ZAP prüfen HTTP-Endpunkte auf Klartextübertragung von Versionsdaten; 
-Wireshark bestätigt Fehlen von TLS</t>
-  </si>
-  <si>
-    <t>Scapy / boofuzz (PROFIsafe iPar/F-Parameter-Fuzzing)</t>
-  </si>
-  <si>
-    <t>Analog RQ-002 – Nachweis, dass modifizierte Parameter bei korrekter CRC nicht erkannt werden</t>
-  </si>
-  <si>
     <t>Einfacher HTTP-GET auf /deviceinfo/swinfo/*-Endpunkte zur Bestätigung der Klartextübertragung</t>
-  </si>
-  <si>
-    <t>Siege (-c 50 -t 10M)</t>
-  </si>
-  <si>
-    <t>Prüft, ob 2-Connection-Limit selbst zu DoS führt (2 Clients halten Verbindung offen)</t>
-  </si>
-  <si>
-    <t>Wireshark mit PROFINET-Dissector (I&amp;M0-Auslese via azyklischem Record 0xAFF0) 
-+ manuelle Debug-Port-Prüfung</t>
-  </si>
-  <si>
-    <t>Da REVISION_COUNTER Teil von I&amp;M0 ist, muss über PROFINET-Records ausgelesen werden, nicht über HTTP</t>
   </si>
   <si>
     <t>Wireshark (I&amp;M0/iParCRC-Vergleich) 
 + curl (Firmware-Version via IoT-Core)</t>
   </si>
   <si>
-    <t>Kombination aus Netzwerk- und Web-Interface nötig, da Requirement beide Kanäle referenziert</t>
-  </si>
-  <si>
     <t>Testet explizit das Fehlen von Rate-Limiting auf dem Feldbus (CR 7.1 RE(1)), das generische Web-DoS-Tools nicht abdecken</t>
   </si>
   <si>
@@ -869,35 +661,107 @@
 + physischer Power-Cycle-Test</t>
   </si>
   <si>
-    <t>curl (Firmware-Version-Endpoint) 
-+ manuelle Dokumentenprüfung (Release Notes vs. geforderter Upload-Log)</t>
-  </si>
-  <si>
-    <t>Verifiziert das dokumentierte Löschen des Logs bei Coldstart gegen die 5-Jahres-Anforderung</t>
-  </si>
-  <si>
-    <t>Kein aktives Pentest-Tool nötig – Gap ist strukturell (fehlendes Feature), Nachweis erfolgt über Dokumentenabgleich</t>
-  </si>
-  <si>
-    <t>Prüft explizit fehlende Auth-Gate vor Zugriff auf Error Log über IoT-Core HTTP</t>
-  </si>
-  <si>
-    <t>curl / OWASP ZAP) 
-+ manueller physischer Bypass-Test (Rotary/DIL-Switch-Zugriff simulieren)
-+ Scapy (PROFINET-Layer)</t>
-  </si>
-  <si>
-    <t>Direkter, unauthentifizierter PUT/POST-Test gegen diese Endpunkte zur Bestätigung des fehlenden Auth-Gates;
-Requirement bezieht sich auf physische Zugangskontrolle, nicht auf ein digitales Login;
-Prüft, ob Schreibzugriffe auf F-Parameter tatsächlich nur nach Param-Begin/Param-End-Kommando möglich sind (SRIO-7749)</t>
-  </si>
-  <si>
     <t>CR 7.8 CR 7.1, CR 7.2</t>
   </si>
   <si>
     <t>SVV1, SVV2, SVV3</t>
   </si>
   <si>
+    <t>curl / Nikto  (evtl. curl ausreichend)</t>
+  </si>
+  <si>
+    <t>Reine Dokumentenprüfung (kein aktiver Test nötig)</t>
+  </si>
+  <si>
+    <t>Schnelle, risikofreie Tests (sofort ausführbar, keine Abhängigkeiten)</t>
+  </si>
+  <si>
+    <t>Fieldbus-Tests mit Infrastruktur-Voraussetzung</t>
+  </si>
+  <si>
+    <t>Physische Tests, sequenzsensitiv</t>
+  </si>
+  <si>
+    <t>Dokumentenprüfung</t>
+  </si>
+  <si>
+    <t>Web/API-Block (keine Abhängigkeiten)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netzwerk-Teil:  I&amp;M0 auslesen  </t>
+  </si>
+  <si>
+    <t>Web-Teil: Web/API-Block (keine Abhängigkeiten)
+Netzwerk-Teil: I&amp;MO auslesen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physischer F-Adress-/Mode-Test + Power-Cycle Prüfen: löscht dieser Cycle bereits das Log? Falls ja → Schritt 4 muss davor liegen </t>
+  </si>
+  <si>
+    <t>Priorisation</t>
+  </si>
+  <si>
+    <t>CRC-Kollisionstests (gebündelt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flood/Fuzzing-Test </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siegel-/Tamper-Test </t>
+  </si>
+  <si>
+    <t>Erzwungener Cold-Start (ZULETZT – zerstört Log-Zustand für dieses Gerät)</t>
+  </si>
+  <si>
+    <t>Freedom from hazard on the non-safety COM/IoT path relies on the assumption ``used in a safe zone behind a firewall'' (SRIO-9402) 
+--&gt; not verifiable by functional testing of the device alone</t>
+  </si>
+  <si>
+    <t>Ist der Non-Safety-Pfad tatsächlich abgeschottet, oder erreicht man unerwartete Dienste/Ports?" (= Prüfung der Firewall-Annahme); 
+Wireshark verifiziert F_Dest_Add/F_Source_Add-und CRC im normalen Betrieb tatsächlich vorhanden sind und wie dokumentiert funktionieren;
+Nachweis, dass F_WD_Time-Watchdog den erwarteten Fallback auslöst</t>
+  </si>
+  <si>
+    <t>CRC-Kollisionsangriff erfordert gezielte Paket-Manipulation 
+1. Gültiges PROFIsafe-Frame abfangen/nachbauen
+2.Prozessdaten-Payload verändern
+3. CRC über die veränderten Daten neu berechnen (nicht die alte CRC beibehalten!)
+4. Frame senden und beobachten, ob die SCPU es akzeptiert), 
+kein Standard-Scanner deckt PROFIsafe-CRC ab
++
+Kann das Gehäuse geöffnet/die Schalterstellung verändert werden, ohne das Siegel sichtbar zu beschädigen (z. B. durch Nachbau/Ablösen und Wiederanbringen)?
+Gibt es einen Weg, über das Gehäuse hinweg (z. B. Bohrung, Wärmeeinwirkung) auf die Schalter zuzugreifen?</t>
+  </si>
+  <si>
+    <t>Scapy (Python, custom PROFINET-Frame-Manipulation) 
++ physische Siegelprüfung (manuell)</t>
+  </si>
+  <si>
+    <t>JTAGulator / Logic-Analyzer (sigrok/PulseView) 
++ manuelle Inspektion
++ curl (IoT-Core /devicestatus/errorlog) 
++ Wireshark (I&amp;M0/REVISION_COUNTER via PROFINET, analog RQ-008/009)</t>
+  </si>
+  <si>
+    <t>1. Schalterstellung an G physisch ändern (dokumentiert, mit Zeitstempel deinerseits)
+2. Sofort danach: Error-Log (curl) und I&amp;M0/REVISION_COUNTER (Wireshark) auslesen
+3. Erwartetes Ergebnis (= Bestätigung des Gaps): kein Eintrag zu dieser Aktion vorhanden → Negativ-Nachweis erbracht
+4. JTAGulator/Logic-Analyzer ergänzend einsetzen, um zu zeigen: selbst wenn ein Angreifer nicht über die Schalter, sondern über ein gefusetes Debug-Interface zugreifen würde, entstünde ebenfalls kein Log-Eintrag – das untermauert die "avoids visible damage"-Aussage im Gap 
+→ Nachweis, dass kein Audit-Eintrag zur physischen G-Aktion entsteht</t>
+  </si>
+  <si>
+    <t>Concrete Tool (Reason)</t>
+  </si>
+  <si>
+    <t>CR 7.8 CR 4.1</t>
+  </si>
+  <si>
+    <t>curl reicht aus, um zu bestätigen, dass /deviceinfo/hwversion, /deviceinfo/swrevision und /deviceinfo/swinfo/scpuversion ohne TLS und ohne Zugriffskontrolle auslesbar sind – ein automatisierter Web-Scanner (Nikto/ZAP) liefert hier keinen zusätzlichen Erkenntnisgewinn, da es sich um einen einzelnen, bekannten Endpunkt-Satz handelt, keine unbekannte Angriffsfläche. Wireshark bestätigt ergänzend auf Protokollebene, dass die Antwort tatsächlich in Klartext (kein TLS-Handshake, kein HTTPS) übertragen wird</t>
+  </si>
+  <si>
+    <r>
+      <t>CR 3.4,</t>
+    </r>
     <r>
       <rPr>
         <i/>
@@ -907,6 +771,150 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve"> EDR 3.14</t>
+    </r>
+  </si>
+  <si>
+    <t>CRC-based check only ;
+no cryptographic signature/HMAC verification (SRSL3-equivalent per prEN 50742 \S7.4.3.4.1 not reached); 
+Additionally, no mechanism (e.g. firmware signing, secure boot) is documented for protecting safety software/firmware (Asset D) against corruption – this part of the requirement appears structurally unaddressed, separate from the CRC-based data-protection gap."</t>
+  </si>
+  <si>
+    <t>Protocol Integrity Testing (Fieldbus, für B) 
++ Firmware Integrity Verification / Documentation Review (für D)</t>
+  </si>
+  <si>
+    <t>CRC-Kollisionsangriff erfordert gezielte Paket-Manipulation 
+1. Gültiges PROFIsafe-Frame abfangen/nachbauen
+2.Prozessdaten-Payload verändern
+3. CRC über die veränderten Daten neu berechnen (nicht die alte CRC beibehalten!)
+4. Frame senden und beobachten, ob die SCPU es akzeptiert), 
+kein Standard-Scanner deckt PROFIsafe-CRC ab
+Scapy weist die CRC-Kollision für Konfigurationsdaten nach (B); 
+Für den Software-Anteil (D) existiert keine beschriebene Mitigation – der Test besteht darin, das Fehlen eines Signatur-/Secure-Boot-Mechanismus zu verifizieren (Firmware-Header-Analyse bzw. Herstellerdokumentation), analog zur SVV-1-Negativbestätigung bei RQ-013.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Scapy (PROFIsafe iPar/F-Parameter-Manipulation, für B)
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+ binwalk/checksec</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + Dokumentenprüfung (für D, Nachweis fehlender Signatur-/Boot-Verifikation)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">H (Availability); 
+D (identification data) </t>
+  </si>
+  <si>
+    <t>curl --no-keepalive in zwei parallelen, absichtlich offengehaltenen Sessions (oder netcat), anschließend dritter Zugriffsversuch → prüft, ob bereits 2 Verbindungen zum vollständigen Ausschluss weiterer Clients führen;
+Tool: einfaches Monitoring-Script (curl in Schleife, z. B. alle 1s) parallel zu einem ausgelösten FW-Update-Vorgang → dokumentiert die tatsächliche Downtime-Dauer der Identifikations-API</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Siege (-c 50 -t 10M);
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>curl</t>
+    </r>
+  </si>
+  <si>
+    <t>D (Safety Firmware);
+G (Operating Mode); 
+I (Audit Data)</t>
+  </si>
+  <si>
+    <t>Zuerst FW-Update-Modus regulär auslösen → I&amp;M0/REVISION_COUNTER prüfen. Danach – falls ein Debug-Zugang trotz Fusing gefunden wird – erneut Error-Log prüfen, ob dieser Zugriff protokolliert wurde (aktuell fehlender Schritt)</t>
+  </si>
+  <si>
+    <t>REVISION_COUNTER increment (I&amp;M0data) on every parameter change 
+provides a basic non-repudiation marker for configuration interventions.</t>
+  </si>
+  <si>
+    <t>REVISION_COUNTER + iParCRC comparison on configuration change; 
+FW/HW compatibility check per component plus Release Notes on firmware change.</t>
+  </si>
+  <si>
+    <r>
+      <t>Wireshark mit PROFINET-Dissector (I&amp;M0-Auslese via azyklischem Record 0xAFF0) 
++ manuelle Debug-Port-Prüfung (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>JTAGulator + Logic-Analyzer (sigrok/PulseView</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>SVV1 (negative confirmation)</t>
+  </si>
+  <si>
+    <t>Zwei unterschiedliche Konfigurationsänderungen nacheinander durchführen (z. B. zwei verschiedene Parameteränderungen an zwei verschiedenen Tagen/durch zwei verschiedene "Personen" simuliert)
+REVISION_COUNTER danach auslesen
+Zeigen: Der Zähler ist zwar inkrementiert (Änderung ist sichtbar), aber es lässt sich nicht unterscheiden, welche der beiden Änderungen wann/durch wen erfolgte – nur "eine Änderung fand statt"</t>
+  </si>
+  <si>
+    <t>REVISION_COUNTER records that a change occurred, but not who performed it or when;
+no timestamp/actor field documented, limiting genuine non-repudiation value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">External hardware watchdog and PROFIsafe F_WD_Time device-acknowledgment watchdog trigger a controlled fallback to a defined failsafe state on communication loss (state transition 9); 
+max. 2 concurrent HTTP connections limit COM/IoT-side resource exhaustion. </t>
+  </si>
+  <si>
+    <t>A (Trusted Safety Function),
+B (PROFINET)
+H (Network),
+(E Safety Monitoring)</t>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Scapy (PROFINET-Flood)  </t>
     </r>
     <r>
@@ -922,28 +930,193 @@
     </r>
   </si>
   <si>
-    <t>Nmap (-sS -sV -p- -oA, UDP-Scan)  wenn möglich ansonsten Scapy (wegen DCP)+ 
-Wireshark (PROFIsafe-Dissector)</t>
-  </si>
-  <si>
-    <t>Nikto + 
-Burp Suite / OWASP ZAP +  (evtl. curl ausreichend)
-Wireshark</t>
-  </si>
-  <si>
-    <t>curl / Nikto  (evtl. curl ausreichend)</t>
-  </si>
-  <si>
-    <t>OWASP ZAP (Active Scan auf Authorization) 
-+ Nikto 
-+ curl  (evtl. curl ausreichend)</t>
+    <t>Tampering, 
+Spoofing, 
+Elevation of Privilege</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I (Audit Data); 
+</t>
+  </si>
+  <si>
+    <t>curl liest den Log-Inhalt vor und nach dem Cold-Start aus und ermöglicht einen direkten Vergleich der Eintragsanzahl/-inhalte. Der physische Power-Cycle ist notwendig, um den bereits dokumentierten Cold-Start-Löschmechanismus reproduzierbar auszulösen. 
+Ein einzelner Testdurchlauf genügt als struktureller Nachweis (ein einmaliges Löschen widerspricht bereits eindeutig der 5-Jahres-Retentionspflicht) – eine tatsächliche Langzeitprüfung über 5 Jahre ist weder praktikabel noch nötig, da der Mechanismus (Löschung bei jedem Cold-Start) bereits als konstant/reproduzierbar dokumentiert ist.</t>
+  </si>
+  <si>
+    <t>curl (Abfrage des Firmware-Version-Endpoints) + 
+manuelle Dokumentenprüfung (Release Notes vs. Anforderung)</t>
+  </si>
+  <si>
+    <t>curl bestätigt, dass die IoT-Core-API ausschließlich die aktuell installierte Firmware-Version zurückliefert, keine historische Abfolge früherer Uploads – dies dient als unterstützender Negativ-Beleg dafür, dass kein geräteresidenter Versions-Tracking-Mechanismus existiert. 
+Der eigentliche Nachweis erfolgt über den manuellen Abgleich der herstellerseitigen Release Notes gegen die Anforderung: Release Notes sind ein externes, nicht geräte-/seriennummer-gebundenes Artefakt ohne garantierte 5-Jahres-Aufbewahrung pro Upload und ohne Manipulationsschutz – sie erfüllen die Anforderung an einen tamper-evident, geräteresidenten Tracing-Log nicht. Kein aktives Pentest-Tool erforderlich, da der Gap strukturell (fehlendes Feature) und nicht durch aktives Testen zusätzlich beweisbar ist.</t>
+  </si>
+  <si>
+    <t>curl (unauthentifizierter GET auf /devicestatus/errorlog)</t>
+  </si>
+  <si>
+    <t>Ein einzelner, gezielter GET-Request genügt, um zu bestätigen, ob der Error-Log-Endpunkt ohne jegliche Authentifizierung/Autorisierung erreichbar ist – die Frage ist binär (Zugriff möglich: ja/nein) und betrifft einen einzigen, bereits bekannten Endpunkt. 
+Ein generischer Scanner (Nikto) oder ein automatisierter Active Scan (ZAP) liefert hier keinen zusätzlichen Erkenntnisgewinn, da keine unbekannte Angriffsfläche exploriert werden muss – analog zur Tool-Begründung bei RQ-004/006/013. Optional könnte ZAP/Nikto ergänzend eingesetzt werden, falls zusätzlich geprüft werden soll, ob weitere, nicht dokumentierte Log-/Debug-Endpunkte existieren – das wäre dann aber ein eigenständiger Explorations-Testzweck, nicht Teil des hier beschriebenen Gap-Nachweises.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nmap (-sS -sV -p- -oA, UDP-Scan) </t>
+  </si>
+  <si>
+    <t>Wireshark (PROFIsafe-Dissector)+
++ Scapy (custom PROFIsafe-Frame mit falscher F_Source_Add senden)</t>
+  </si>
+  <si>
+    <t>curl (gezielte GET-Requests gegen die vier Endpunkte) + Wireshark (Traffic-Capture des HTTP-Austauschs)</t>
+  </si>
+  <si>
+    <t>scapy weist den zentralen Gap direkt nach: Da laut Dokumentation die Autorisierung für Parameterschreibzugriffe vollständig auf den physischen Rotary/DIL-Switch-Zugang (Asset G) delegiert ist und CR 1.1/1.2/2.1 nicht auf dem Gerät selbst durchgesetzt werden, muss geprüft werden, ob ein reiner Netzwerkangreifer – ohne physischen Zugriff auf die Schalter – trotzdem ein gültiges Param-Begin/Write/Param-End-Frame senden kann und die SCPU dieses akzeptiert. Ein positiver Befund (Frame wird verarbeitet) bestätigt, dass die physische Barriere die einzige wirksame Kontrolle ist und durch reine Protokollkenntnis umgangen werden kann.
+curl/ZAP testen ergänzend den IoT-Core-HTTP-Pfad auf fehlende Auth-Gates; da IoT-Core dokumentiert als Read-Only ausgelegt ist, wird hier ein negatives Ergebnis erwartet (kein Schreibzugriff möglich) – der Test dient der Bestätigung, dass dieser Pfad korrekt abgesichert ist, nicht dem Nachweis des eigentlichen Gaps.
+Der physische Bypass-Test prüft unabhängig davon, ob die Schalterstellung selbst ohne sichtbare Beschädigung verändert werden kann (Asset G), um auszuschließen, dass die als "physische Barriere" angenommene Kontrolle in der Praxis leicht umgangen werden kann.
+pnio_dcp/profi-dcp bietet eine direkte High-Level-Funktion für den Factory-Reset-Request (DCPControlBlock), ohne manuellen Frame-Aufbau. Wireshark bestätigt anhand der "Set OK"-Response, ob der Reset tatsächlich ausgeführt wurde. Test bestätigt denselben normativen Gap wie RQ-011, diesmal über den Netzwerk- statt den Fieldbus-Parametrierungspfad.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Identification data is transmitted only via unencrypted HTTP (HTTPS/Websocket/MQTT explicitly unsupported);
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">secondary Information Disclosure risk on the physical Ethernet interface (reconnaissance of exact FW/HW versions);
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Identifikationspflicht umfasst Software und Daten; nur Software (D) wird identifiziert, Daten/Config (B) bleibt unadressiert"</t>
+    </r>
+  </si>
+  <si>
+    <t>B (Config), 
+D (Configuration/Parameter Integrity, runtime)</t>
+  </si>
+  <si>
+    <t>scapy (custom PROFINET-Layer: Param-Begin/Write/Param-End-Sequenz gemäß SRIO-7749, gesendet ohne vorherigen physischen Rotary/DIL-Switch-Zugriff) 
++curl / OWASP ZAP (unauthentifizierter PUT/POST gegen IoT-Core-Parametrierungs-Endpunkte) 
++ manueller physischer Bypass-Test (Rotary/DIL-Switch-Zugriff ohne sichtbare Manipulation simulieren) 
++ pnio_dcp / profi-dcp (Python) oder Scapy (scapy.contrib.pnio_dcp) + Wireshark (Response-Verifikation)
++FW-Update-Mode-Entry-Testlücke (Wireshark-Referenzaufzeichnung des legitimen Trigger-Signals + Scapy-Replay ohne physischen Schalter),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Disclosure; 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Disclosurey;
+</t>
+  </si>
+  <si>
+    <r>
+      <t>Major finding: password protection for safety-parameter writes was explicitly dropped ; 
+IoT-Core was made read-only instead. 
+Parameter writes are only possible via the fieldbus/PLC engineering tool; 
+authorization is fully delegated to an external, unverified assumption (locked control cabinet, restricted network access). 
+CR 1.1/1.2/2.1 are therefore not enforced on the device itself. 
+Additionally, no mechanism exists for learning-phase settings;
+DCP "Reset to Factory" operiert auf Layer 2 und ist laut PROFINET-Spezifikation grundsätzlich unauthentifiziert; ein Netzwerkteilnehmer im selben Segment kann sicherheitsrelevante Konfiguration (Mode 3/4) zurücksetzen, ohne die physische Rotary/DIL-Switch-Barriere zu berühren – identischer Kern-Gap wie RQ-011 (fehlende geräteseitige Autorisierung), über einen zweiten, unabhängigen Angriffspfad bestätig</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tBei RQ-011 wird der DCP-Factory-Reset als "grundsätzlich unauthentifiziert" bezeichnet. Das ist eine allgemeine PROFINET-Protokolleigenschaft, aber ich finde in den SRIO-Dokumenten keinen expliziten Beleg, dass SRIO hier keine zusätzliche Absicherung implementiert (SRIO-7772/SRIO-3030 beschreiben nur die Reset-Modi selbst, nicht deren Authentifizierung). Das sollte als "auf allgemeinem Protokollwissen basierend, im Test zu verifizieren" gekennzeichnet werden, nicht als bereits gesicherte Tatsache</t>
+    </r>
+  </si>
+  <si>
+    <t>Protocol Integrity  (Fieldbus-specific); 
+Physical Interface Testing (Tamper)</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Tests</t>
+  </si>
+  <si>
+    <t>Begründung</t>
+  </si>
+  <si>
+    <t>Web/API-Block (RQ-004,006,007-Teil,009-web,014)</t>
+  </si>
+  <si>
+    <t>vollständig passiv/reversibel, schnelle Ergebnisse</t>
+  </si>
+  <si>
+    <t>Netzwerk-Scan/Sniffing (RQ-001), I&amp;M0-Reads (RQ-008,009)</t>
+  </si>
+  <si>
+    <t>passiv, keine Zustandsänderung</t>
+  </si>
+  <si>
+    <t>Dokumentenprüfung (RQ-013)</t>
+  </si>
+  <si>
+    <t>parallelisierbar, keine Geräteinteraktion</t>
+  </si>
+  <si>
+    <t>CRC-Kollisionstests (RQ-002,005)</t>
+  </si>
+  <si>
+    <t>aktiv, aber i. d. R. durch Fallback erholbar</t>
+  </si>
+  <si>
+    <t>Physische Testkampagne konsolidiert (RQ-003+RQ-011, ggf. RQ-002-Siegelteil)</t>
+  </si>
+  <si>
+    <t>teils irreversibel (Siegel) – nach den harmlosen Tests</t>
+  </si>
+  <si>
+    <t>Flood/Fuzzing (RQ-010)</t>
+  </si>
+  <si>
+    <t>hohes Instabilitätsrisiko – bewusst vor dem finalen Schritt</t>
+  </si>
+  <si>
+    <t>Erzwungener Cold-Start (RQ-012)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">irreversibel, zerstört Log – </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>letzter Schritt</t>
+    </r>
+  </si>
+  <si>
+    <t>Netzwerk-Scan/Sniffing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -985,6 +1158,33 @@
       <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1028,7 +1228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1036,20 +1236,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1060,11 +1248,296 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1079,6 +1552,27 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5EAFDBE1-CA5A-4392-829A-64428D2E4A96}" name="Tabelle1" displayName="Tabelle1" ref="B3:M17" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="B3:M17" xr:uid="{5EAFDBE1-CA5A-4392-829A-64428D2E4A96}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{9794DB0A-B324-4851-8A32-F076AD6D9DC3}" name="MVO-ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{DDA27BB5-BAE4-44BD-A799-A77FD76C5131}" name="IEC 62443 CR" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{AC477F4C-62BB-43C5-89FF-4BBADFEFD1A4}" name="Target Asset" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{EA04613D-7CEF-40D3-8F07-5ED9819A33B1}" name="Threat (STRIDE)" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{7014F427-582A-4962-BA61-3C6C9AC27C85}" name="Security Function (Mitigation)" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{319A09E4-9642-436F-B2D1-CBC9CA516833}" name="Gap" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{7566DA89-BEC1-4A9A-B807-30D8EE04BDBD}" name="SVV Category" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{23906E4B-C21C-4D1A-82AF-4ED95F2E7372}" name="Target Interface Type" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{0CA5A5FD-7DB5-481E-9F83-AE6061EA4BD9}" name="Tool  Category" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{078A3E20-0A95-47A8-8F42-1B94AB3210F4}" name="Concrete Tool" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{8C510399-577C-4B6E-98E5-F84607316C2E}" name="Concrete Tool (Reason)" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{275C9993-7621-4D40-99F5-375FA4B68AE5}" name="Priorisation" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1398,589 +1892,686 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB352A9E-FA09-4936-805B-24B06A598CDB}">
-  <dimension ref="B3:Q68"/>
+  <dimension ref="B2:Q68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.42578125" style="1"/>
-    <col min="3" max="4" width="29.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="78.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="54" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="42.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="41" style="1" customWidth="1"/>
-    <col min="11" max="11" width="48.28515625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="37.140625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="42.28515625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="25.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="22" style="1" customWidth="1"/>
-    <col min="17" max="17" width="33.7109375" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="2" width="11.42578125" style="9"/>
+    <col min="3" max="3" width="15.28515625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="68.28515625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="48" style="9" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="9" customWidth="1"/>
+    <col min="9" max="9" width="27.85546875" style="9" customWidth="1"/>
+    <col min="10" max="10" width="31.42578125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="39.5703125" style="9" customWidth="1"/>
+    <col min="12" max="12" width="76.42578125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="42.28515625" style="9" customWidth="1"/>
+    <col min="14" max="14" width="56.42578125" style="9" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" style="9" customWidth="1"/>
+    <col min="16" max="16" width="22" style="9" customWidth="1"/>
+    <col min="17" max="17" width="33.7109375" style="9" customWidth="1"/>
+    <col min="18" max="16384" width="11.42578125" style="9"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
+    <row r="2" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="213.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F5" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="197.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="O6" s="5">
+        <v>3</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="145.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="O7" s="5">
+        <v>4</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="235.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="O8" s="5">
+        <v>5</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="O9" s="5">
+        <v>6</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="182.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="O10" s="5">
+        <v>7</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" ht="132" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" ht="408.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" ht="162" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" ht="189.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" ht="192" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" ht="258" x14ac:dyDescent="0.25">
+      <c r="E19" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="K3" s="6" t="s">
+      <c r="J19" s="11" t="s">
         <v>131</v>
-      </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="P3" s="4"/>
-    </row>
-    <row r="4" spans="2:17" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="2:17" ht="93" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" spans="2:17" ht="99" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" spans="2:17" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="M7" s="2"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-    </row>
-    <row r="8" spans="2:17" ht="87.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="M8" s="2"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-    </row>
-    <row r="9" spans="2:17" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="M9" s="2"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-    </row>
-    <row r="10" spans="2:17" ht="72" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="M10" s="2"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-    </row>
-    <row r="11" spans="2:17" ht="75" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="M11" s="2"/>
-    </row>
-    <row r="12" spans="2:17" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="M12" s="2"/>
-    </row>
-    <row r="13" spans="2:17" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" spans="2:17" ht="189" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="M14" s="2"/>
-    </row>
-    <row r="15" spans="2:17" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="M15" s="2"/>
-    </row>
-    <row r="16" spans="2:17" ht="90" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" spans="2:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="19" spans="2:13" ht="258" x14ac:dyDescent="0.25">
-      <c r="E19" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="66" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -1992,12 +2583,15 @@
   <headerFooter>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 INTERNAL</oddFooter>
   </headerFooter>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D436C63D-BC80-4342-876E-1B6D43B6666C}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2010,10 +2604,10 @@
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -2021,10 +2615,10 @@
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -2032,10 +2626,10 @@
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -2043,23 +2637,23 @@
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -2067,10 +2661,10 @@
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -2078,10 +2672,10 @@
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -2089,10 +2683,10 @@
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -2121,10 +2715,10 @@
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -2132,10 +2726,10 @@
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -2143,10 +2737,10 @@
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -2154,10 +2748,10 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -2165,10 +2759,10 @@
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -2176,10 +2770,10 @@
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -2187,23 +2781,23 @@
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -2211,10 +2805,10 @@
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -2222,10 +2816,10 @@
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -2233,10 +2827,10 @@
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -2244,10 +2838,10 @@
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -2255,10 +2849,10 @@
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -2266,10 +2860,10 @@
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -2277,10 +2871,10 @@
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -2291,7 +2885,7 @@
         <v>19</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -2324,100 +2918,112 @@
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="B39" s="2"/>
-    </row>
-    <row r="40" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J39" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
-      <c r="B40" s="8"/>
-    </row>
-    <row r="41" spans="1:2" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="4"/>
+      <c r="J40" s="9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B41" s="8"/>
-    </row>
-    <row r="42" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+      <c r="B41" s="4"/>
+    </row>
+    <row r="42" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
-      <c r="B42" s="8"/>
-    </row>
-    <row r="43" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="4"/>
+    </row>
+    <row r="43" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
-      <c r="B43" s="8"/>
-    </row>
-    <row r="44" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="B43" s="4"/>
+    </row>
+    <row r="44" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="B44" s="2"/>
     </row>
-    <row r="45" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="B45" s="2"/>
     </row>
-    <row r="46" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="150" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="B48" s="2"/>
     </row>
     <row r="49" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="B49" s="2"/>
     </row>
     <row r="50" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/Asset-Mapping.xlsx
+++ b/Asset-Mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifmworld-my.sharepoint.com/personal/nathalie_nuber_ifm_com/Documents/Documents/DHBW/Bachelorarbeit/Bachelorarbeit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1177" documentId="8_{7646D5EB-5A7E-4C2C-B298-2CCD9ED2279B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A6B79AE-5AF1-4863-89D9-F98107862183}"/>
+  <xr:revisionPtr revIDLastSave="1186" documentId="8_{7646D5EB-5A7E-4C2C-B298-2CCD9ED2279B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3F4C7F8-9E1F-44B6-ABFF-EB69D37E5AEC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A49BA81-CDEC-4679-BB9D-EFEA5E788525}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A49BA81-CDEC-4679-BB9D-EFEA5E788525}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="237">
   <si>
     <t>MVO-ID</t>
   </si>
@@ -318,12 +318,6 @@
 D</t>
   </si>
   <si>
-    <t>SVV3</t>
-  </si>
-  <si>
-    <t>SVV1</t>
-  </si>
-  <si>
     <t>A (Trusted Safety Function); 
 F (Domain Separation)</t>
   </si>
@@ -439,9 +433,6 @@
 direct conflict with the ``exclusively for authority request'' restriction of RQ-014.</t>
   </si>
   <si>
-    <t>SVV Category</t>
-  </si>
-  <si>
     <t>Target Interface Type</t>
   </si>
   <si>
@@ -449,18 +440,6 @@
   </si>
   <si>
     <t>Concrete Tool</t>
-  </si>
-  <si>
-    <t>SVV2, SVV3</t>
-  </si>
-  <si>
-    <t>SVV-1 (negative confirmation)</t>
-  </si>
-  <si>
-    <t>SVV1, SVV3</t>
-  </si>
-  <si>
-    <t>SVV1, SVV4</t>
   </si>
   <si>
     <t xml:space="preserve">Network (PROFINET record data); 
@@ -664,9 +643,6 @@
     <t>CR 7.8 CR 7.1, CR 7.2</t>
   </si>
   <si>
-    <t>SVV1, SVV2, SVV3</t>
-  </si>
-  <si>
     <t>curl / Nikto  (evtl. curl ausreichend)</t>
   </si>
   <si>
@@ -711,10 +687,6 @@
   </si>
   <si>
     <t>Erzwungener Cold-Start (ZULETZT – zerstört Log-Zustand für dieses Gerät)</t>
-  </si>
-  <si>
-    <t>Freedom from hazard on the non-safety COM/IoT path relies on the assumption ``used in a safe zone behind a firewall'' (SRIO-9402) 
---&gt; not verifiable by functional testing of the device alone</t>
   </si>
   <si>
     <t>Ist der Non-Safety-Pfad tatsächlich abgeschottet, oder erreicht man unerwartete Dienste/Ports?" (= Prüfung der Firewall-Annahme); 
@@ -890,9 +862,6 @@
       </rPr>
       <t>)</t>
     </r>
-  </si>
-  <si>
-    <t>SVV1 (negative confirmation)</t>
   </si>
   <si>
     <t>Zwei unterschiedliche Konfigurationsänderungen nacheinander durchführen (z. B. zwei verschiedene Parameteränderungen an zwei verschiedenen Tagen/durch zwei verschiedene "Personen" simuliert)
@@ -1111,12 +1080,29 @@
   <si>
     <t>Netzwerk-Scan/Sniffing</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Freedom from hazard on the non-safety COM/IoT path relies on the assumption ``used in a safe zone behind a firewall'' (SRIO-9402) 
+--&gt; not verifiable by functional testing of the device alone
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SRIO-7830 – GSD FPar Address Type:"Safe Remote IO shall support Address Type 1." Und explizit definiert:"Address Type 1 if F_DestAdd is checked only" (im Gegensatz zu Address Type 2, wo zusätzlich F_SourceAdd geprüft wird)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1158,13 +1144,6 @@
       <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1228,7 +1207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1251,45 +1230,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <font>
         <b val="0"/>
@@ -1555,16 +1509,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5EAFDBE1-CA5A-4392-829A-64428D2E4A96}" name="Tabelle1" displayName="Tabelle1" ref="B3:M17" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="B3:M17" xr:uid="{5EAFDBE1-CA5A-4392-829A-64428D2E4A96}"/>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{9794DB0A-B324-4851-8A32-F076AD6D9DC3}" name="MVO-ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{DDA27BB5-BAE4-44BD-A799-A77FD76C5131}" name="IEC 62443 CR" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{AC477F4C-62BB-43C5-89FF-4BBADFEFD1A4}" name="Target Asset" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{EA04613D-7CEF-40D3-8F07-5ED9819A33B1}" name="Threat (STRIDE)" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{7014F427-582A-4962-BA61-3C6C9AC27C85}" name="Security Function (Mitigation)" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{319A09E4-9642-436F-B2D1-CBC9CA516833}" name="Gap" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{7566DA89-BEC1-4A9A-B807-30D8EE04BDBD}" name="SVV Category" dataDxfId="5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5EAFDBE1-CA5A-4392-829A-64428D2E4A96}" name="Tabelle1" displayName="Tabelle1" ref="B3:L17" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="B3:L17" xr:uid="{5EAFDBE1-CA5A-4392-829A-64428D2E4A96}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{9794DB0A-B324-4851-8A32-F076AD6D9DC3}" name="MVO-ID" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{DDA27BB5-BAE4-44BD-A799-A77FD76C5131}" name="IEC 62443 CR" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{AC477F4C-62BB-43C5-89FF-4BBADFEFD1A4}" name="Target Asset" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{EA04613D-7CEF-40D3-8F07-5ED9819A33B1}" name="Threat (STRIDE)" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{7014F427-582A-4962-BA61-3C6C9AC27C85}" name="Security Function (Mitigation)" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{319A09E4-9642-436F-B2D1-CBC9CA516833}" name="Gap" dataDxfId="5"/>
     <tableColumn id="8" xr3:uid="{23906E4B-C21C-4D1A-82AF-4ED95F2E7372}" name="Target Interface Type" dataDxfId="4"/>
     <tableColumn id="9" xr3:uid="{0CA5A5FD-7DB5-481E-9F83-AE6061EA4BD9}" name="Tool  Category" dataDxfId="3"/>
     <tableColumn id="10" xr3:uid="{078A3E20-0A95-47A8-8F42-1B94AB3210F4}" name="Concrete Tool" dataDxfId="2"/>
@@ -1892,30 +1845,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB352A9E-FA09-4936-805B-24B06A598CDB}">
-  <dimension ref="B2:Q68"/>
+  <dimension ref="B2:P68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.42578125" style="9"/>
-    <col min="3" max="3" width="15.28515625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" style="9" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="68.28515625" style="9" customWidth="1"/>
-    <col min="7" max="7" width="48" style="9" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="9" customWidth="1"/>
-    <col min="9" max="9" width="27.85546875" style="9" customWidth="1"/>
-    <col min="10" max="10" width="31.42578125" style="9" customWidth="1"/>
-    <col min="11" max="11" width="39.5703125" style="9" customWidth="1"/>
-    <col min="12" max="12" width="76.42578125" style="9" customWidth="1"/>
-    <col min="13" max="13" width="42.28515625" style="9" customWidth="1"/>
-    <col min="14" max="14" width="56.42578125" style="9" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" style="9" customWidth="1"/>
-    <col min="16" max="16" width="22" style="9" customWidth="1"/>
-    <col min="17" max="17" width="33.7109375" style="9" customWidth="1"/>
-    <col min="18" max="16384" width="11.42578125" style="9"/>
+    <col min="1" max="2" width="11.42578125" style="1"/>
+    <col min="3" max="3" width="15.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="68.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="48" style="1" customWidth="1"/>
+    <col min="8" max="8" width="35.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="27.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="31.42578125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="68" style="1" customWidth="1"/>
+    <col min="12" max="12" width="76.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="42.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="56.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="22" style="1" customWidth="1"/>
+    <col min="17" max="17" width="33.7109375" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1932,646 +1885,601 @@
         <v>83</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>177</v>
+      <c r="K3" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>218</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="4" spans="2:17" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E4" s="8" t="s">
+      <c r="D4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="O4" s="5">
+      <c r="F4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="N4" s="5">
         <v>1</v>
       </c>
+      <c r="O4" s="5" t="s">
+        <v>221</v>
+      </c>
       <c r="P4" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="5" spans="2:17" ht="213.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" ht="213.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="O5" s="5">
+      <c r="H5" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="N5" s="5">
         <v>2</v>
       </c>
+      <c r="O5" s="5" t="s">
+        <v>223</v>
+      </c>
       <c r="P5" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17" ht="197.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" ht="197.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="O6" s="5">
+      <c r="H6" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="N6" s="5">
         <v>3</v>
       </c>
+      <c r="O6" s="5" t="s">
+        <v>225</v>
+      </c>
       <c r="P6" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" ht="145.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" ht="145.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="C7" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="O7" s="5">
+      <c r="E7" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N7" s="5">
         <v>4</v>
       </c>
+      <c r="O7" s="5" t="s">
+        <v>227</v>
+      </c>
       <c r="P7" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" ht="235.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="12" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" ht="235.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="E8" s="8" t="s">
+      <c r="C8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="O8" s="5">
+      <c r="F8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="N8" s="5">
         <v>5</v>
       </c>
+      <c r="O8" s="5" t="s">
+        <v>229</v>
+      </c>
       <c r="P8" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="O9" s="5">
+      <c r="E9" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="N9" s="5">
         <v>6</v>
       </c>
+      <c r="O9" s="5" t="s">
+        <v>231</v>
+      </c>
       <c r="P9" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="10" spans="2:17" ht="182.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" ht="182.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="L10" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="O10" s="5">
+      <c r="N10" s="5">
         <v>7</v>
       </c>
+      <c r="O10" s="5" t="s">
+        <v>233</v>
+      </c>
       <c r="P10" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="11" spans="2:17" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="E11" s="8" t="s">
+      <c r="D11" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="12" spans="2:17" ht="132" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F11" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="132" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" ht="408.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="2:17" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="14" spans="2:17" ht="408.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" s="8" t="s">
+      <c r="G14" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="15" spans="2:17" ht="162" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L14" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="162" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="D15" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" ht="189.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="E16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="K15" s="8" t="s">
+      <c r="G16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="L15" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="16" spans="2:17" ht="189.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="F16" s="8" t="s">
+    </row>
+    <row r="17" spans="2:12" ht="192" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="E17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" ht="192" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" ht="258" x14ac:dyDescent="0.25">
-      <c r="E19" s="10" t="s">
+      <c r="H17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="258" x14ac:dyDescent="0.25">
+      <c r="E19" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="J19" s="11" t="s">
-        <v>131</v>
+      <c r="J19" s="9" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="66" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2920,53 +2828,53 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="J37" s="9" t="s">
-        <v>168</v>
+        <v>133</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>169</v>
+        <v>136</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B39" s="2"/>
-      <c r="J39" s="9" t="s">
-        <v>170</v>
+      <c r="J39" s="1" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="4"/>
-      <c r="J40" s="9" t="s">
-        <v>171</v>
+      <c r="J40" s="1" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B41" s="4"/>
     </row>
@@ -2980,50 +2888,50 @@
     </row>
     <row r="44" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B44" s="2"/>
     </row>
     <row r="45" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B45" s="2"/>
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B48" s="2"/>
     </row>
     <row r="49" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B49" s="2"/>
     </row>
     <row r="50" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/Asset-Mapping.xlsx
+++ b/Asset-Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifmworld-my.sharepoint.com/personal/nathalie_nuber_ifm_com/Documents/Documents/DHBW/Bachelorarbeit/Bachelorarbeit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1186" documentId="8_{7646D5EB-5A7E-4C2C-B298-2CCD9ED2279B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3F4C7F8-9E1F-44B6-ABFF-EB69D37E5AEC}"/>
+  <xr:revisionPtr revIDLastSave="1261" documentId="8_{7646D5EB-5A7E-4C2C-B298-2CCD9ED2279B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C74F57A2-BA5D-435F-970C-F908939E1BA5}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A49BA81-CDEC-4679-BB9D-EFEA5E788525}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="241">
   <si>
     <t>MVO-ID</t>
   </si>
@@ -325,37 +325,7 @@
     <t>Gap</t>
   </si>
   <si>
-    <t>C (Process Data),
-G (Rotary Switches- OP-Mode)</t>
-  </si>
-  <si>
-    <t>PROFIsafe frame-level 4-byte CRC and iParCRC/F\_ParCRC detect corruption of transmitted safety data; 
-physical plastic/metal seals on rotary/DIL switch housings provide tamper resistance for the physical F-address interface.</t>
-  </si>
-  <si>
-    <t>CRC provides accidental-corruption detection only, not cryptographic authentication,  
-an attacker able to recompute a matching CRC over modified data is not detected, 
-although RQ-002 explicitly requires protection against both accidental and intentional corruption</t>
-  </si>
-  <si>
-    <t>G (Rotary Switches - OP-Mode)
-I (Audit Data)</t>
-  </si>
-  <si>
     <t>N.I</t>
-  </si>
-  <si>
-    <t>only physical seal + visual inspection exist; 
-no automatic hardware-tamper logging. 
-Illegitimate intervention that avoids visible damage remains unrecorded and unattributable.</t>
-  </si>
-  <si>
-    <t>Version-identification API via IoT-Core 
-(/deviceinfo/hwversion, /deviceinfo/swrevision, /deviceinfo/swinfo/scpuversion).</t>
-  </si>
-  <si>
-    <t>iParCRC / F\_ParCRC checksum verification of safety configuration 
-and process parameters, checked by SCPU each parametrization cycle.</t>
   </si>
   <si>
     <t>Software inventory read-out via IoT-Core 
@@ -442,18 +412,7 @@
     <t>Concrete Tool</t>
   </si>
   <si>
-    <t xml:space="preserve">Network (PROFINET record data); 
-Physical (Rotary/DIL switch housing) </t>
-  </si>
-  <si>
-    <t>Physical 
-(Rotary/DIL switch, Debug/Test interface)</t>
-  </si>
-  <si>
     <t>Web/API (IoT-Core HTTP)</t>
-  </si>
-  <si>
-    <t>Network (PROFIsafe iPar/F-Parameter)</t>
   </si>
   <si>
     <t>Network (PROFINET/PROFIsafe); 
@@ -468,9 +427,6 @@
   </si>
   <si>
     <t xml:space="preserve">Web/API (IoT-Core HTTP) </t>
-  </si>
-  <si>
-    <t>Network (Ethernet (IEEE 802.3u), DCP, IPv4, TCP (via HTTP))</t>
   </si>
   <si>
     <t>Tool Category = f(SVV-Kategorie, Interface-Typ)</t>
@@ -574,12 +530,6 @@
 Web/API (IoT-Core, /devicestatus/errorlog)</t>
   </si>
   <si>
-    <t>PROFIsafe black-channel: 
-F\_Dest\_Add/F\_Source\_Add address verification, 
-4-byte CRC per safety frame, 
-While F_WD_Time watchdog detects loss of timely communication (staleness), triggering a fallback to Parametrization before a corrupted or misdirected frame's effect can reach the safety logic (SCPU)</t>
-  </si>
-  <si>
     <t>Network Discovery / Port &amp; Service Identification; 
 Network Sniffing / Protocol Analysis</t>
   </si>
@@ -633,13 +583,6 @@
 + curl (Firmware-Version via IoT-Core)</t>
   </si>
   <si>
-    <t>Testet explizit das Fehlen von Rate-Limiting auf dem Feldbus (CR 7.1 RE(1)), das generische Web-DoS-Tools nicht abdecken</t>
-  </si>
-  <si>
-    <t>curl/Burp (Query /devicestatus/errorlog vor/nach Power-Cycle) 
-+ physischer Power-Cycle-Test</t>
-  </si>
-  <si>
     <t>CR 7.8 CR 7.1, CR 7.2</t>
   </si>
   <si>
@@ -677,58 +620,16 @@
     <t>Priorisation</t>
   </si>
   <si>
-    <t>CRC-Kollisionstests (gebündelt)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Flood/Fuzzing-Test </t>
   </si>
   <si>
-    <t xml:space="preserve">Siegel-/Tamper-Test </t>
-  </si>
-  <si>
     <t>Erzwungener Cold-Start (ZULETZT – zerstört Log-Zustand für dieses Gerät)</t>
   </si>
   <si>
-    <t>Ist der Non-Safety-Pfad tatsächlich abgeschottet, oder erreicht man unerwartete Dienste/Ports?" (= Prüfung der Firewall-Annahme); 
-Wireshark verifiziert F_Dest_Add/F_Source_Add-und CRC im normalen Betrieb tatsächlich vorhanden sind und wie dokumentiert funktionieren;
-Nachweis, dass F_WD_Time-Watchdog den erwarteten Fallback auslöst</t>
-  </si>
-  <si>
-    <t>CRC-Kollisionsangriff erfordert gezielte Paket-Manipulation 
-1. Gültiges PROFIsafe-Frame abfangen/nachbauen
-2.Prozessdaten-Payload verändern
-3. CRC über die veränderten Daten neu berechnen (nicht die alte CRC beibehalten!)
-4. Frame senden und beobachten, ob die SCPU es akzeptiert), 
-kein Standard-Scanner deckt PROFIsafe-CRC ab
-+
-Kann das Gehäuse geöffnet/die Schalterstellung verändert werden, ohne das Siegel sichtbar zu beschädigen (z. B. durch Nachbau/Ablösen und Wiederanbringen)?
-Gibt es einen Weg, über das Gehäuse hinweg (z. B. Bohrung, Wärmeeinwirkung) auf die Schalter zuzugreifen?</t>
-  </si>
-  <si>
-    <t>Scapy (Python, custom PROFINET-Frame-Manipulation) 
-+ physische Siegelprüfung (manuell)</t>
-  </si>
-  <si>
-    <t>JTAGulator / Logic-Analyzer (sigrok/PulseView) 
-+ manuelle Inspektion
-+ curl (IoT-Core /devicestatus/errorlog) 
-+ Wireshark (I&amp;M0/REVISION_COUNTER via PROFINET, analog RQ-008/009)</t>
-  </si>
-  <si>
-    <t>1. Schalterstellung an G physisch ändern (dokumentiert, mit Zeitstempel deinerseits)
-2. Sofort danach: Error-Log (curl) und I&amp;M0/REVISION_COUNTER (Wireshark) auslesen
-3. Erwartetes Ergebnis (= Bestätigung des Gaps): kein Eintrag zu dieser Aktion vorhanden → Negativ-Nachweis erbracht
-4. JTAGulator/Logic-Analyzer ergänzend einsetzen, um zu zeigen: selbst wenn ein Angreifer nicht über die Schalter, sondern über ein gefusetes Debug-Interface zugreifen würde, entstünde ebenfalls kein Log-Eintrag – das untermauert die "avoids visible damage"-Aussage im Gap 
-→ Nachweis, dass kein Audit-Eintrag zur physischen G-Aktion entsteht</t>
-  </si>
-  <si>
     <t>Concrete Tool (Reason)</t>
   </si>
   <si>
     <t>CR 7.8 CR 4.1</t>
-  </si>
-  <si>
-    <t>curl reicht aus, um zu bestätigen, dass /deviceinfo/hwversion, /deviceinfo/swrevision und /deviceinfo/swinfo/scpuversion ohne TLS und ohne Zugriffskontrolle auslesbar sind – ein automatisierter Web-Scanner (Nikto/ZAP) liefert hier keinen zusätzlichen Erkenntnisgewinn, da es sich um einen einzelnen, bekannten Endpunkt-Satz handelt, keine unbekannte Angriffsfläche. Wireshark bestätigt ergänzend auf Protokollebene, dass die Antwort tatsächlich in Klartext (kein TLS-Handshake, kein HTTPS) übertragen wird</t>
   </si>
   <si>
     <r>
@@ -744,51 +645,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> EDR 3.14</t>
-    </r>
-  </si>
-  <si>
-    <t>CRC-based check only ;
-no cryptographic signature/HMAC verification (SRSL3-equivalent per prEN 50742 \S7.4.3.4.1 not reached); 
-Additionally, no mechanism (e.g. firmware signing, secure boot) is documented for protecting safety software/firmware (Asset D) against corruption – this part of the requirement appears structurally unaddressed, separate from the CRC-based data-protection gap."</t>
-  </si>
-  <si>
-    <t>Protocol Integrity Testing (Fieldbus, für B) 
-+ Firmware Integrity Verification / Documentation Review (für D)</t>
-  </si>
-  <si>
-    <t>CRC-Kollisionsangriff erfordert gezielte Paket-Manipulation 
-1. Gültiges PROFIsafe-Frame abfangen/nachbauen
-2.Prozessdaten-Payload verändern
-3. CRC über die veränderten Daten neu berechnen (nicht die alte CRC beibehalten!)
-4. Frame senden und beobachten, ob die SCPU es akzeptiert), 
-kein Standard-Scanner deckt PROFIsafe-CRC ab
-Scapy weist die CRC-Kollision für Konfigurationsdaten nach (B); 
-Für den Software-Anteil (D) existiert keine beschriebene Mitigation – der Test besteht darin, das Fehlen eines Signatur-/Secure-Boot-Mechanismus zu verifizieren (Firmware-Header-Analyse bzw. Herstellerdokumentation), analog zur SVV-1-Negativbestätigung bei RQ-013.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Scapy (PROFIsafe iPar/F-Parameter-Manipulation, für B)
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>+ binwalk/checksec</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> + Dokumentenprüfung (für D, Nachweis fehlender Signatur-/Boot-Verifikation)</t>
     </r>
   </si>
   <si>
@@ -864,11 +720,6 @@
     </r>
   </si>
   <si>
-    <t>Zwei unterschiedliche Konfigurationsänderungen nacheinander durchführen (z. B. zwei verschiedene Parameteränderungen an zwei verschiedenen Tagen/durch zwei verschiedene "Personen" simuliert)
-REVISION_COUNTER danach auslesen
-Zeigen: Der Zähler ist zwar inkrementiert (Änderung ist sichtbar), aber es lässt sich nicht unterscheiden, welche der beiden Änderungen wann/durch wen erfolgte – nur "eine Änderung fand statt"</t>
-  </si>
-  <si>
     <t>REVISION_COUNTER records that a change occurred, but not who performed it or when;
 no timestamp/actor field documented, limiting genuine non-repudiation value.</t>
   </si>
@@ -908,71 +759,16 @@
 </t>
   </si>
   <si>
-    <t>curl liest den Log-Inhalt vor und nach dem Cold-Start aus und ermöglicht einen direkten Vergleich der Eintragsanzahl/-inhalte. Der physische Power-Cycle ist notwendig, um den bereits dokumentierten Cold-Start-Löschmechanismus reproduzierbar auszulösen. 
-Ein einzelner Testdurchlauf genügt als struktureller Nachweis (ein einmaliges Löschen widerspricht bereits eindeutig der 5-Jahres-Retentionspflicht) – eine tatsächliche Langzeitprüfung über 5 Jahre ist weder praktikabel noch nötig, da der Mechanismus (Löschung bei jedem Cold-Start) bereits als konstant/reproduzierbar dokumentiert ist.</t>
-  </si>
-  <si>
-    <t>curl (Abfrage des Firmware-Version-Endpoints) + 
-manuelle Dokumentenprüfung (Release Notes vs. Anforderung)</t>
-  </si>
-  <si>
-    <t>curl bestätigt, dass die IoT-Core-API ausschließlich die aktuell installierte Firmware-Version zurückliefert, keine historische Abfolge früherer Uploads – dies dient als unterstützender Negativ-Beleg dafür, dass kein geräteresidenter Versions-Tracking-Mechanismus existiert. 
-Der eigentliche Nachweis erfolgt über den manuellen Abgleich der herstellerseitigen Release Notes gegen die Anforderung: Release Notes sind ein externes, nicht geräte-/seriennummer-gebundenes Artefakt ohne garantierte 5-Jahres-Aufbewahrung pro Upload und ohne Manipulationsschutz – sie erfüllen die Anforderung an einen tamper-evident, geräteresidenten Tracing-Log nicht. Kein aktives Pentest-Tool erforderlich, da der Gap strukturell (fehlendes Feature) und nicht durch aktives Testen zusätzlich beweisbar ist.</t>
-  </si>
-  <si>
     <t>curl (unauthentifizierter GET auf /devicestatus/errorlog)</t>
   </si>
   <si>
-    <t>Ein einzelner, gezielter GET-Request genügt, um zu bestätigen, ob der Error-Log-Endpunkt ohne jegliche Authentifizierung/Autorisierung erreichbar ist – die Frage ist binär (Zugriff möglich: ja/nein) und betrifft einen einzigen, bereits bekannten Endpunkt. 
-Ein generischer Scanner (Nikto) oder ein automatisierter Active Scan (ZAP) liefert hier keinen zusätzlichen Erkenntnisgewinn, da keine unbekannte Angriffsfläche exploriert werden muss – analog zur Tool-Begründung bei RQ-004/006/013. Optional könnte ZAP/Nikto ergänzend eingesetzt werden, falls zusätzlich geprüft werden soll, ob weitere, nicht dokumentierte Log-/Debug-Endpunkte existieren – das wäre dann aber ein eigenständiger Explorations-Testzweck, nicht Teil des hier beschriebenen Gap-Nachweises.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nmap (-sS -sV -p- -oA, UDP-Scan) </t>
-  </si>
-  <si>
-    <t>Wireshark (PROFIsafe-Dissector)+
-+ Scapy (custom PROFIsafe-Frame mit falscher F_Source_Add senden)</t>
-  </si>
-  <si>
-    <t>curl (gezielte GET-Requests gegen die vier Endpunkte) + Wireshark (Traffic-Capture des HTTP-Austauschs)</t>
   </si>
   <si>
     <t>scapy weist den zentralen Gap direkt nach: Da laut Dokumentation die Autorisierung für Parameterschreibzugriffe vollständig auf den physischen Rotary/DIL-Switch-Zugang (Asset G) delegiert ist und CR 1.1/1.2/2.1 nicht auf dem Gerät selbst durchgesetzt werden, muss geprüft werden, ob ein reiner Netzwerkangreifer – ohne physischen Zugriff auf die Schalter – trotzdem ein gültiges Param-Begin/Write/Param-End-Frame senden kann und die SCPU dieses akzeptiert. Ein positiver Befund (Frame wird verarbeitet) bestätigt, dass die physische Barriere die einzige wirksame Kontrolle ist und durch reine Protokollkenntnis umgangen werden kann.
 curl/ZAP testen ergänzend den IoT-Core-HTTP-Pfad auf fehlende Auth-Gates; da IoT-Core dokumentiert als Read-Only ausgelegt ist, wird hier ein negatives Ergebnis erwartet (kein Schreibzugriff möglich) – der Test dient der Bestätigung, dass dieser Pfad korrekt abgesichert ist, nicht dem Nachweis des eigentlichen Gaps.
 Der physische Bypass-Test prüft unabhängig davon, ob die Schalterstellung selbst ohne sichtbare Beschädigung verändert werden kann (Asset G), um auszuschließen, dass die als "physische Barriere" angenommene Kontrolle in der Praxis leicht umgangen werden kann.
 pnio_dcp/profi-dcp bietet eine direkte High-Level-Funktion für den Factory-Reset-Request (DCPControlBlock), ohne manuellen Frame-Aufbau. Wireshark bestätigt anhand der "Set OK"-Response, ob der Reset tatsächlich ausgeführt wurde. Test bestätigt denselben normativen Gap wie RQ-011, diesmal über den Netzwerk- statt den Fieldbus-Parametrierungspfad.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Identification data is transmitted only via unencrypted HTTP (HTTPS/Websocket/MQTT explicitly unsupported);
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">secondary Information Disclosure risk on the physical Ethernet interface (reconnaissance of exact FW/HW versions);
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Identifikationspflicht umfasst Software und Daten; nur Software (D) wird identifiziert, Daten/Config (B) bleibt unadressiert"</t>
-    </r>
-  </si>
-  <si>
-    <t>B (Config), 
-D (Configuration/Parameter Integrity, runtime)</t>
   </si>
   <si>
     <t>scapy (custom PROFINET-Layer: Param-Begin/Write/Param-End-Sequenz gemäß SRIO-7749, gesendet ohne vorherigen physischen Rotary/DIL-Switch-Zugriff) 
@@ -983,10 +779,6 @@
   </si>
   <si>
     <t xml:space="preserve">Information Disclosure; 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Disclosurey;
 </t>
   </si>
   <si>
@@ -1081,6 +873,43 @@
     <t>Netzwerk-Scan/Sniffing</t>
   </si>
   <si>
+    <t>“Is the non-safety path actually isolated, or can unexpected services/ports be accessed?” (= Verification of the firewall assumption);
+Wireshark verifies that F_Dest_Add, F_Source_Add, and CRC are actually present during normal operation and function as documented;
+Verification that the F_WD_Time watchdog triggers the expected fallback</t>
+  </si>
+  <si>
+    <t>A single, targeted GET request is sufficient to confirm whether the error log endpoint is accessible without any authentication or authorization—the question is binary (access possible: yes/no) and concerns a single, already known endpoint.
+A generic scanner (Nikto) or an automated active scan (ZAP) does not provide any additional insights here, since there is no unknown attack surface to explore—similar to the rationale for the tools in RQ-004/006/013. Optionally, ZAP or Nikto could be used as a supplement if it is necessary to additionally verify whether other, undocumented log/debug endpoints exist—but that would then constitute a separate exploratory testing objective, not part of the gap verification described here.</t>
+  </si>
+  <si>
+    <t>curl (querying the firmware version endpoint) +
+manual document review (release notes vs. requirements)</t>
+  </si>
+  <si>
+    <t>curl confirms that the IoT Core API returns only the currently installed firmware version, not a historical sequence of previous uploads—this serves as supporting evidence that no device-resident version-tracking mechanism exists.
+The actual proof is provided by manually comparing the manufacturer’s release notes against the requirement: Release notes are an external artifact not tied to a specific device or serial number, with no guaranteed 5-year retention period per upload and no protection against tampering—they do not meet the requirement for a tamper-evident, device-resident tracing log. No active penetration testing tool is required, as the gap is structural (missing feature) and can be further verified without active testing.</t>
+  </si>
+  <si>
+    <t>curl reads the log contents before and after the cold start and allows for a direct comparison of the number and content of entries. The physical power cycle is necessary to reliably trigger the cold-start deletion mechanism that has already been documented.
+A single test run is sufficient as structural evidence (a one-time deletion already clearly contradicts the 5-year retention requirement)—an actual long-term test spanning 5 years is neither practical nor necessary, since the mechanism (deletion at every cold start) has already been documented as consistent and reproducible.</t>
+  </si>
+  <si>
+    <t>curl/Burp (Query /devicestatus/errorlog before/after a power cycle)
++ Physical power cycle test</t>
+  </si>
+  <si>
+    <t>Explicitly tests for the absence of rate limiting on the fieldbus (CR 7.1 RE(1)), which generic Web DoS tools do not cover</t>
+  </si>
+  <si>
+    <t>Perform two different configuration changes one after the other (e.g., two different parameter changes simulated on two different days or by two different “people”)
+Read the REVISION_COUNTER afterward
+Result: Although the counter has been incremented (the change is visible), it is impossible to distinguish which of the two changes occurred when or by whom—only that “a change took place”</t>
+  </si>
+  <si>
+    <t>PROFIsafe black‑channel: F_Dest_Add verification (Address Type 1, F_Source_Add present but unchecked), 4‑byte CRC (CRC‑Seed24/32) per safety frame, F_WD_Time watchdog., 
+While F_WD_Time watchdog detects loss of timely communication (staleness), triggers passivation to the defined safe state (outputs Low, qualifier bad); re‑integration requires acknowledgment."</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Freedom from hazard on the non-safety COM/IoT path relies on the assumption ``used in a safe zone behind a firewall'' (SRIO-9402) 
 --&gt; not verifiable by functional testing of the device alone
@@ -1089,20 +918,210 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>SRIO-7830 – GSD FPar Address Type:"Safe Remote IO shall support Address Type 1." Und explizit definiert:"Address Type 1 if F_DestAdd is checked only" (im Gegensatz zu Address Type 2, wo zusätzlich F_SourceAdd geprüft wird)</t>
+      <t>SRIO-7830 – GSD FPar Address Type:"Safe Remote IO shall support Address Type 1." And :"Address Type 1 if F_DestAdd is checked only" (unlike Address Type 2, where F_SourceAdd is also checked),  because F_Source_Add is unchecked under Address Type 1, a frame with a forged source cannot be rejected on that basis ,  so the only barrier is the external firewall assumption, which is not verifiable by device‑level functional testing</t>
     </r>
+  </si>
+  <si>
+    <t>(a) PROFIsafe frame: Ethernet L2 / PROFINET RT 0x8892 ; 
+(b) Non‑safe path: DCP (L2), IPv4/TCP/HTTP (IoT‑Core).</t>
+  </si>
+  <si>
+    <t>nmap (isolation/exposure) 
++ Wireshark PROFIsafe dissector (passive field verification) 
++ Scapy (active F_Source_Add spoof)</t>
+  </si>
+  <si>
+    <t>C (Transmitted Safety Frame),
+G (physical F-address interface)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(a) Network — cyclic PROFIsafe frame, Ethernet L2 / PROFINET RT 0x8892 (process-data CRC); 
+(b) Network — acyclic PROFINET record data (iPar/F-Parameter CRC); 
+(c) Physical — rotary/DIL switch housing (seal), separate physical bench </t>
+  </si>
+  <si>
+    <t>Scapy (active, on Pi — capture, modify payload, recompute CRC, re-inject) 
++ Wireshark PROFIsafe dissector (passive capture of a valid reference frame);
+ manual seal inspection (separate physical bench).</t>
+  </si>
+  <si>
+    <t>CRC-collision attack requires targeted packet manipulation: 
+(1) capture/rebuild a valid PROFIsafe frame; 
+(2) alter the process-data payload; 
+(3) recompute the CRC over the modified data (do NOT keep the old CRC); 
+(4) inject and observe whether the SCPU accepts it.
+Physical: can the housing be opened / switch position changed without visibly damaging the seal (detach + re-apply)? Is there a way to reach the switches through the housing (drilling, heat)?</t>
+  </si>
+  <si>
+    <t>CRC-collision tests (bundled with RQ-005)</t>
+  </si>
+  <si>
+    <t>PROFIsafe frame-level 4-byte CRC (CRC-Seed24/32) detects corruption of the transmitted safety frame; iParCRC (UINT32) and F_ParCRC (UINT16) protect the parameter transfer (engineering tool → F-Device); 
+physical plastic/metal seals on the rotary/DIL switch housing provide tamper resistance for the physical F-address interface</t>
+  </si>
+  <si>
+    <t>The CRC provides accidental-corruption detection only, not cryptographic authentication (no signature/HMAC). An attacker who recomputes a matching CRC over modified process data is not detected, whereas RQ-002 explicitly requires protection against both accidental AND intentional corruption. 
+The physical interface relies on visual seal integrity only, with no automatic tamper evidence</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">G (Physical F-address/OP-mode interface);
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="3" tint="0.499984740745262"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Debug&amp; Testinterface</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+I (Audit Data)</t>
+    </r>
+  </si>
+  <si>
+    <t>physical plastic/metal seal + visual inspection only. 
+No automatic hardware-tamper logging or tamper-evidence record is generated by the device.</t>
+  </si>
+  <si>
+    <t>Only physical seal + visual inspection exist; no automatic hardware-tamper logging. 
+An illegitimate intervention that avoids visible seal damage remains unrecorded and unattributable, so CR 2.8/2.12 (auditable event + non-repudiation) are not met for physical interventions. 
+The debug/test port is disabled by fusing (design exclusion), not evidenced by a log entry as RQ-003 would strictly require</t>
+  </si>
+  <si>
+    <t>(a) Physical — rotary/DIL switch + debug/test port (separate physical bench);
+(b) Audit read-back: Web/API (IoT-Core HTTP, /devicestatus/errorlog) and Network (PROFINET acyclic I&amp;M0, 0xAFF0 / REVISION_COUNTER)</t>
+  </si>
+  <si>
+    <t>(1) Physically change switch position G (document with your own timestamp).
+(2) Immediately read the error log (curl) and I&amp;M0/REVISION_COUNTER (Wireshark). 
+(3) Expected result (= gap confirmation): no entry referencing this physical action → negative proof delivered. 
+(4) Optionally use JTAGulator/logic-analyzer to show that even access via a fused debug interface would produce no log entry,  reinforcing the "avoids visible damage" statement in the Gap.</t>
+  </si>
+  <si>
+    <t>Seal / tamper test (physical bench); 
+audit read-back part fits the Web/API + I&amp;M0 block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tampering (primary );
+ Information Disclosure (secondary)
+</t>
+  </si>
+  <si>
+    <t>Version/identification API via IoT-Core: 
+/deviceinfo/hwversion, /deviceinfo/hwrevision, /deviceinfo/swrevision, /deviceinfo/swinfo/scpuversion, /deviceinfo/swinfo/cpubootloaderversion, /deviceinfo/swinfo/scpubootloaderversion. 
+Provides software/firmware identification (asset D)</t>
+  </si>
+  <si>
+    <t>Primary (identification completeness): the identification obligation covers software AND data. Only software/firmware (D) is identified via the API;
+configuration/data (B) is not addressed → RQ-004 only partially met. 
+Secondary (confidentiality): identification data is transmitted only via unencrypted HTTP (HTTPS/Websocket/MQTT explicitly unsupported), enabling reconnaissance of exact FW/HW versions on the Ethernet interface</t>
+  </si>
+  <si>
+    <t>Web/API - IoT-Core HTTP (identification read-out); 
+Network - IPv4/TCP/HTTP cleartext (passive sniffing of the same exchange)</t>
+  </si>
+  <si>
+    <t>curl (targeted GET requests against the /deviceinfo endpoints) 
++ Wireshark (passive capture of the HTTP exchange, mirror port). 
+Nikto/ZAP N/A.  a single, known endpoint set is no unknown attack surface, so an automated web scanner adds no insight</t>
+  </si>
+  <si>
+    <t>curl is sufficient to confirm that /deviceinfo/hwversion, /deviceinfo/swrevision and /deviceinfo/swinfo/scpuversion are readable without TLS and without access control; an automated web scanner (Nikto/ZAP) yields no additional insight for a single known endpoint set. 
+Wireshark additionally confirms at protocol level that the response is transmitted in cleartext (no TLS handshake, no HTTPS). For the primary objective, curl also verifies whether any endpoint identifies configuration/data (B) ; expected result: none exists (gap confirmation).</t>
+  </si>
+  <si>
+    <t>Web/API block (no dependencies)</t>
+  </si>
+  <si>
+    <t>B (Runtime integrity), 
+D (image integrity)</t>
+  </si>
+  <si>
+    <t>Part B: iParCRC (UINT32) + F_ParCRC (UINT16) checksum verification of safety configuration and process parameters, checked by the SCPU each parametrization cycle. 
+Part D: no documented firmware-signing / secure-boot mechanism for the safety firmware/software.</t>
+  </si>
+  <si>
+    <t>Part B: CRC-based integrity check only; no cryptographic signature/HMAC (SRSL3-equivalent per prEN 50742 §7.4.3.4.1 not reached). An attacker who recomputes iParCRC/F_ParCRC over modified parameters is not detected, although RQ-005 requires protection against both accidental AND intentional corruption.
+ Part D: no mechanism (firmware signing, secure boot) is documented for protecting the safety firmware/software (asset D) against corruption,  this part appears structurally unaddressed, separate from the CRC-based data-protection gap</t>
+  </si>
+  <si>
+    <t>Part B: Network — PROFINET acyclic record data (iPar/F-Parameter, index 0x200 / 0x30n). 
+Part D: FW-Update path (IoT-Core /firmware container) + firmware image analysis (structural/documentation review)</t>
+  </si>
+  <si>
+    <t>B: Protocol Integrity Testing (fieldbus). 
+Part D: Firmware Integrity Verification / Documentation Review (structural negative proof)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">curl (IoT-Core /devicestatus/errorlog) 
++ Wireshark (I&amp;M0 / REVISION_COUNTER via PROFINET acyclic 0xAFF0). 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="3" tint="0.499984740745262"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Optional (separate physical bench): 
+JTAGulator / logic-analyzer (sigrok/PulseView) 
++ manual seal inspection</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Part B: Scapy (PROFIsafe iPar/F-Parameter manipulation with recomputed CRC). 
+Part D: documentation/design review (negative proof of missing signing/secure boot);
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="3" tint="0.499984740745262"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>optionally binwalk (firmware header/entropy) IF a firmware image is obtainable — checksec largely N/A for the bare-metal STM32 safety firmware. nmap/standard scanners N/A for both.)</t>
+    </r>
+  </si>
+  <si>
+    <t>Part B (CRC-collision requires targeted packet manipulation):
+(1) capture/rebuild a valid parameter transfer; 
+(2) modify a safety parameter; 
+(3) recompute iParCRC/F_ParCRC over the modified data (do NOT keep the old CRC); 
+(4) send between param-begin/param-end and observe whether the SCPU accepts it. 
+Part D: no mitigation is described for the software part,  the test consists of verifying the ABSENCE of a signing/secure-boot mechanism (firmware-header analysis and/or manufacturer documentation), analogous to the SVV-1 negative confirmation used at RQ-013</t>
+  </si>
+  <si>
+    <t>CRC-collision tests (bundled with RQ-002); 
+Part D as separate structural/documentation review</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1165,6 +1184,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="3" tint="0.499984740745262"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3" tint="0.499984740745262"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1207,7 +1249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1237,6 +1279,15 @@
       <alignment vertical="center" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1524,7 +1575,7 @@
     <tableColumn id="11" xr3:uid="{8C510399-577C-4B6E-98E5-F84607316C2E}" name="Concrete Tool (Reason)" dataDxfId="1"/>
     <tableColumn id="12" xr3:uid="{275C9993-7621-4D40-99F5-375FA4B68AE5}" name="Priorisation" dataDxfId="0"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1853,12 +1904,11 @@
     <col min="4" max="4" width="21.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="68.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="48" style="1" customWidth="1"/>
-    <col min="8" max="8" width="35.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="27.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="31.42578125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="68" style="1" customWidth="1"/>
-    <col min="12" max="12" width="76.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="68.42578125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="35.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="37.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="74.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="51.5703125" style="1" customWidth="1"/>
     <col min="13" max="13" width="42.28515625" style="1" customWidth="1"/>
     <col min="14" max="14" width="56.42578125" style="1" customWidth="1"/>
     <col min="15" max="15" width="23.7109375" style="1" customWidth="1"/>
@@ -1888,31 +1938,31 @@
         <v>88</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>218</v>
+        <v>182</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="182.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1926,40 +1976,40 @@
         <v>77</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>123</v>
+        <v>210</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>207</v>
+        <v>176</v>
       </c>
       <c r="N4" s="5">
         <v>1</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>221</v>
+        <v>185</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="5" spans="2:16" ht="213.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" ht="165" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1967,176 +2017,176 @@
         <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>89</v>
+        <v>212</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>78</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>90</v>
+        <v>217</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>91</v>
+        <v>218</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>115</v>
+        <v>213</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>217</v>
+        <v>181</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>176</v>
+        <v>214</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>175</v>
+        <v>215</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>170</v>
+        <v>216</v>
       </c>
       <c r="N5" s="5">
         <v>2</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>224</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="2:16" ht="197.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="10" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>92</v>
+        <v>219</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>93</v>
+        <v>220</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>221</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>116</v>
+        <v>222</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>177</v>
+        <v>237</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>172</v>
+        <v>224</v>
       </c>
       <c r="N6" s="5">
         <v>3</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>226</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="2:16" ht="145.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>50</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>95</v>
+        <v>226</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>117</v>
+        <v>228</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>181</v>
+        <v>230</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>165</v>
+        <v>231</v>
       </c>
       <c r="N7" s="5">
         <v>4</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="2:16" ht="235.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="13" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>78</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>96</v>
+        <v>233</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>118</v>
+        <v>235</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>184</v>
+        <v>236</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>185</v>
+        <v>239</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>170</v>
+        <v>240</v>
       </c>
       <c r="N8" s="5">
         <v>5</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>229</v>
+        <v>193</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>230</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="2:16" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="11" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -2146,190 +2196,190 @@
         <v>55</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="K9" s="2" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="N9" s="5">
         <v>6</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="2:16" ht="182.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="N10" s="5">
         <v>7</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="2:16" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="2:16" ht="132" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="2:16" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="K13" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="L13" s="2" t="s">
-        <v>171</v>
-      </c>
     </row>
     <row r="14" spans="2:16" ht="408.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -2339,133 +2389,133 @@
         <v>66</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>216</v>
+        <v>180</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="2:16" ht="162" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="J15" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>173</v>
-      </c>
     </row>
     <row r="16" spans="2:16" ht="189.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="12" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="J16" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="L16" s="2" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="2:12" ht="192" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>81</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="258" x14ac:dyDescent="0.25">
@@ -2479,7 +2529,7 @@
         <v>86</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="66" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2828,53 +2878,53 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="J38" s="1" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B39" s="2"/>
       <c r="J39" s="1" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="4"/>
       <c r="J40" s="1" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B41" s="4"/>
     </row>
@@ -2888,50 +2938,50 @@
     </row>
     <row r="44" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B44" s="2"/>
     </row>
     <row r="45" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B45" s="2"/>
     </row>
     <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B48" s="2"/>
     </row>
     <row r="49" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B49" s="2"/>
     </row>
     <row r="50" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/Asset-Mapping.xlsx
+++ b/Asset-Mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50d0cb2a5a70756e/Studium/DHBW/T3300/Bachelorarbeit/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifmworld-my.sharepoint.com/personal/nathalie_nuber_ifm_com/Documents/Documents/DHBW/Bachelorarbeit/Bachelorarbeit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{67C771C2-39B1-4E7D-ABF9-CEC1F090999D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2852E152-03BE-470C-A965-E0DFC93738BE}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{67C771C2-39B1-4E7D-ABF9-CEC1F090999D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{921E1CD0-001A-4765-9DF2-10B9A9D077B1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4A49BA81-CDEC-4679-BB9D-EFEA5E788525}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A49BA81-CDEC-4679-BB9D-EFEA5E788525}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="243">
   <si>
     <t>MVO-ID</t>
   </si>
@@ -589,35 +589,6 @@
 I (Audit Data)</t>
   </si>
   <si>
-    <t>REVISION_COUNTER + iParCRC comparison on configuration change; 
-FW/HW compatibility check per component plus Release Notes on firmware change.</t>
-  </si>
-  <si>
-    <t>REVISION_COUNTER records that a change occurred, but not who performed it or when;
-no timestamp/actor field documented, limiting genuine non-repudiation value.</t>
-  </si>
-  <si>
-    <t>Web/API (IoT-Core HTTP, firmware version only); 
-Network (PROFINET acyclic/I&amp;M0 records, for REVISION_COUNTER)</t>
-  </si>
-  <si>
-    <t>Log/Audit Review (Protocoll-Layer);
-Web Application Analysis</t>
-  </si>
-  <si>
-    <t>Wireshark (I&amp;M0/iParCRC-Vergleich) 
-+ curl (Firmware-Version via IoT-Core)</t>
-  </si>
-  <si>
-    <t>Perform two different configuration changes one after the other (e.g., two different parameter changes simulated on two different days or by two different “people”)
-Read the REVISION_COUNTER afterward
-Result: Although the counter has been incremented (the change is visible), it is impossible to distinguish which of the two changes occurred when or by whom—only that “a change took place”</t>
-  </si>
-  <si>
-    <t>Web-Teil: Web/API-Block (keine Abhängigkeiten)
-Netzwerk-Teil: I&amp;MO auslesen</t>
-  </si>
-  <si>
     <t>RQ-010</t>
   </si>
   <si>
@@ -630,52 +601,10 @@
 (E Safety Monitoring)</t>
   </si>
   <si>
-    <t xml:space="preserve">External hardware watchdog and PROFIsafe F_WD_Time device-acknowledgment watchdog trigger a controlled fallback to a defined failsafe state on communication loss (state transition 9); 
-max. 2 concurrent HTTP connections limit COM/IoT-side resource exhaustion. </t>
-  </si>
-  <si>
-    <t>Mitigations address loss/staleness of communication, not a deliberate flooding/DoS attack on the PROFINET stack itself ;
-no rate-limiting or flood-protection (cf. CR 7.1 RE(1)) documented for the fieldbus interface.</t>
-  </si>
-  <si>
-    <t>Network (PROFINET/PROFIsafe); 
-Physical (Power supply)</t>
-  </si>
-  <si>
-    <t>Network DoS/ Flood Testing;
-Fuzzing Framework (Fieldbus)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Scapy (PROFINET-Flood)  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-+ boofuzz (Protokoll-Fuzzing)</t>
-    </r>
-  </si>
-  <si>
-    <t>Explicitly tests for the absence of rate limiting on the fieldbus (CR 7.1 RE(1)), which generic Web DoS tools do not cover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flood/Fuzzing-Test </t>
-  </si>
-  <si>
     <t>RQ-011</t>
   </si>
   <si>
     <t>CR 1.1, CR 1.2, CR 2.1 (2), CR 3.4</t>
-  </si>
-  <si>
-    <t>B (Safety Config), 
-G (Operating Mode)</t>
   </si>
   <si>
     <t>Tampering, 
@@ -683,123 +612,17 @@
 Elevation of Privilege</t>
   </si>
   <si>
-    <t>F-Address change and FW-Update mode entry require physical access to the rotary/DIL switches plus a power-cycle;
-a physical-presence barrier for these two specific actions.</t>
-  </si>
-  <si>
-    <r>
-      <t>Major finding: password protection for safety-parameter writes was explicitly dropped ; 
-IoT-Core was made read-only instead. 
-Parameter writes are only possible via the fieldbus/PLC engineering tool; 
-authorization is fully delegated to an external, unverified assumption (locked control cabinet, restricted network access). 
-CR 1.1/1.2/2.1 are therefore not enforced on the device itself. 
-Additionally, no mechanism exists for learning-phase settings;
-DCP "Reset to Factory" operiert auf Layer 2 und ist laut PROFINET-Spezifikation grundsätzlich unauthentifiziert; ein Netzwerkteilnehmer im selben Segment kann sicherheitsrelevante Konfiguration (Mode 3/4) zurücksetzen, ohne die physische Rotary/DIL-Switch-Barriere zu berühren – identischer Kern-Gap wie RQ-011 (fehlende geräteseitige Autorisierung), über einen zweiten, unabhängigen Angriffspfad bestätig</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tBei RQ-011 wird der DCP-Factory-Reset als "grundsätzlich unauthentifiziert" bezeichnet. Das ist eine allgemeine PROFINET-Protokolleigenschaft, aber ich finde in den SRIO-Dokumenten keinen expliziten Beleg, dass SRIO hier keine zusätzliche Absicherung implementiert (SRIO-7772/SRIO-3030 beschreiben nur die Reset-Modi selbst, nicht deren Authentifizierung). Das sollte als "auf allgemeinem Protokollwissen basierend, im Test zu verifizieren" gekennzeichnet werden, nicht als bereits gesicherte Tatsache</t>
-    </r>
-  </si>
-  <si>
-    <t>Network (PROFINET/PROFIsafe records); 
-Physical (Rotary/DIL switch)</t>
-  </si>
-  <si>
     <t>Authentication &amp; Authorization Testing
 Physical Access Testing</t>
   </si>
   <si>
-    <t>scapy (custom PROFINET-Layer: Param-Begin/Write/Param-End-Sequenz gemäß SRIO-7749, gesendet ohne vorherigen physischen Rotary/DIL-Switch-Zugriff) 
-+curl / OWASP ZAP (unauthentifizierter PUT/POST gegen IoT-Core-Parametrierungs-Endpunkte) 
-+ manueller physischer Bypass-Test (Rotary/DIL-Switch-Zugriff ohne sichtbare Manipulation simulieren) 
-+ pnio_dcp / profi-dcp (Python) oder Scapy (scapy.contrib.pnio_dcp) + Wireshark (Response-Verifikation)
-+FW-Update-Mode-Entry-Testlücke (Wireshark-Referenzaufzeichnung des legitimen Trigger-Signals + Scapy-Replay ohne physischen Schalter),</t>
-  </si>
-  <si>
-    <t>scapy weist den zentralen Gap direkt nach: Da laut Dokumentation die Autorisierung für Parameterschreibzugriffe vollständig auf den physischen Rotary/DIL-Switch-Zugang (Asset G) delegiert ist und CR 1.1/1.2/2.1 nicht auf dem Gerät selbst durchgesetzt werden, muss geprüft werden, ob ein reiner Netzwerkangreifer – ohne physischen Zugriff auf die Schalter – trotzdem ein gültiges Param-Begin/Write/Param-End-Frame senden kann und die SCPU dieses akzeptiert. Ein positiver Befund (Frame wird verarbeitet) bestätigt, dass die physische Barriere die einzige wirksame Kontrolle ist und durch reine Protokollkenntnis umgangen werden kann.
-curl/ZAP testen ergänzend den IoT-Core-HTTP-Pfad auf fehlende Auth-Gates; da IoT-Core dokumentiert als Read-Only ausgelegt ist, wird hier ein negatives Ergebnis erwartet (kein Schreibzugriff möglich) – der Test dient der Bestätigung, dass dieser Pfad korrekt abgesichert ist, nicht dem Nachweis des eigentlichen Gaps.
-Der physische Bypass-Test prüft unabhängig davon, ob die Schalterstellung selbst ohne sichtbare Beschädigung verändert werden kann (Asset G), um auszuschließen, dass die als "physische Barriere" angenommene Kontrolle in der Praxis leicht umgangen werden kann.
-pnio_dcp/profi-dcp bietet eine direkte High-Level-Funktion für den Factory-Reset-Request (DCPControlBlock), ohne manuellen Frame-Aufbau. Wireshark bestätigt anhand der "Set OK"-Response, ob der Reset tatsächlich ausgeführt wurde. Test bestätigt denselben normativen Gap wie RQ-011, diesmal über den Netzwerk- statt den Fieldbus-Parametrierungspfad.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Physischer F-Adress-/Mode-Test + Power-Cycle Prüfen: löscht dieser Cycle bereits das Log? Falls ja → Schritt 4 muss davor liegen </t>
-  </si>
-  <si>
     <t>RQ-012</t>
   </si>
   <si>
     <t>CR 2.8, CR 2.9</t>
   </si>
   <si>
-    <t xml:space="preserve">I (Audit Data); 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-volatile circular buffer log (≥100 entries, survives non-cold-start resets) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirmed non-conformity: 
-log is explicitly cleared on every coldstart and capacity is fixed at &gt;100 entries;
-both conflict directly with the 5-year retention mandate of RQ-012. </t>
-  </si>
-  <si>
-    <t>Physical (power cycle); 
-Web/API (IoT-Core, /devicestatus/errorlog)</t>
-  </si>
-  <si>
-    <t>Data Persistence/ Retention Testing;
-Physical Interface Testing (Power Cycle)</t>
-  </si>
-  <si>
-    <t>curl/Burp (Query /devicestatus/errorlog before/after a power cycle)
-+ Physical power cycle test</t>
-  </si>
-  <si>
-    <t>curl reads the log contents before and after the cold start and allows for a direct comparison of the number and content of entries. The physical power cycle is necessary to reliably trigger the cold-start deletion mechanism that has already been documented.
-A single test run is sufficient as structural evidence (a one-time deletion already clearly contradicts the 5-year retention requirement)—an actual long-term test spanning 5 years is neither practical nor necessary, since the mechanism (deletion at every cold start) has already been documented as consistent and reproducible.</t>
-  </si>
-  <si>
-    <t>Erzwungener Cold-Start (ZULETZT – zerstört Log-Zustand für dieses Gerät)</t>
-  </si>
-  <si>
     <t>RQ-013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I (Audit Data); 
-D </t>
-  </si>
-  <si>
-    <t>Current firmware version readable via IoT-Core; 
-manufacturer-hosted release notes document version history per release.</t>
-  </si>
-  <si>
-    <t>Release notes are a manufacturer/website artifact, not a device-resident, tamper-evident, per-device upload log with timestamps retained 5 years per upload as literally required; 
-prEN 50742 \S7.3.1 explicitly excludes SW version storage from the tracing log.</t>
-  </si>
-  <si>
-    <t>Web/API (IoT-Core, firmware version)</t>
-  </si>
-  <si>
-    <t>Information Disclosure/ Documentation Review;
-Web Application Analysis</t>
-  </si>
-  <si>
-    <t>curl (querying the firmware version endpoint) +
-manual document review (release notes vs. requirements)</t>
-  </si>
-  <si>
-    <t>curl confirms that the IoT Core API returns only the currently installed firmware version, not a historical sequence of previous uploads—this serves as supporting evidence that no device-resident version-tracking mechanism exists.
-The actual proof is provided by manually comparing the manufacturer’s release notes against the requirement: Release notes are an external artifact not tied to a specific device or serial number, with no guaranteed 5-year retention period per upload and no protection against tampering—they do not meet the requirement for a tamper-evident, device-resident tracing log. No active penetration testing tool is required, as the gap is structural (missing feature) and can be further verified without active testing.</t>
-  </si>
-  <si>
-    <t>Dokumentenprüfung</t>
   </si>
   <si>
     <t>RQ-014</t>
@@ -1147,6 +970,243 @@
       </rPr>
       <t xml:space="preserve">F (unauthenticated cleartext exposure channel) </t>
     </r>
+  </si>
+  <si>
+    <t>Configuration change: REVISION_COUNTER (I&amp;M0) increments and iParCRC/F_ParCRC change on parameter modification. 
+Firmware change: FW/HW compatibility check per component + error-log entry;
+ manufacturer-hosted Release Notes document version history per release.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> REVISION_COUNTER records THAT a change occurred, but not WHO performed it or WHEN , no actor or timestamp field is documented, limiting genuine non-repudiation. 
+Error-log entries evidencing modification reside in a circular buffer cleared on coldstart, so the evidence is not durably retained. Release Notes are an external artifact, not a device-resident, per-device modification record.</t>
+  </si>
+  <si>
+    <t>Web/API -  IoT-Core HTTP (firmware version + /devicestatus/errorlog);
+Network - PROFINET acyclic I&amp;M0 (0xAFF0, REVISION_COUNTER) + iParCRC comparison</t>
+  </si>
+  <si>
+    <t>Log/Audit Review (protocol layer 
++ API); Web Application Analysis</t>
+  </si>
+  <si>
+    <t>Wireshark PROFINET dissector (I&amp;M0/REVISION_COUNTER + iParCRC comparison via acyclic 0xAFF0) 
++ curl (firmware version 
++ /devicestatus/errorlog via IoT-Core). nmap/scanners N/A — known endpoints, structural finding.</t>
+  </si>
+  <si>
+    <t>Perform two different configuration changes one after the other (e.g., two different parameter changes, simulated as if on two different days or by two different "people"). 
+Read the REVISION_COUNTER (and iParCRC) afterward. 
+Result: although the counter has incremented (the change is visible), it is impossible to distinguish which of the two changes occurred, when, or by whom,  only that "a change took place." curl additionally confirms only the current FW version is exposed, not a modification history.</t>
+  </si>
+  <si>
+    <t>Web/API part: Web/API block (no dependencies); 
+Network part: read I&amp;M0 (I&amp;M0 block)</t>
+  </si>
+  <si>
+    <t>Denial of Service (primary);
+Tampering (malformed-frame fuzzing)</t>
+  </si>
+  <si>
+    <t>External hardware watchdog + PROFIsafe F_WD_Time device-acknowledgment watchdog trigger a controlled passivation to the defined fail-safe state on communication loss/staleness (fail-safe transition). 
+Max. 2 concurrent HTTP connections limit COM/IoT-side resource exhaustion.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mitigations address loss/staleness of communication, not a deliberate flooding/DoS or malformed-frame attack on the PROFINET stack itself. 
+No rate-limiting or flood-protection (cf. CR 7.1 RE(1)) is documented for the fieldbus interface,  based on general PROFINET/stack knowledge, to be verified by test. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Note: even if flooding only forces repeated passivation, continuous unavailability of the safety function is itself an availability impact under RQ-010.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Network:  PROFINET/PROFIsafe (L2, EtherType 0x8892) - primary. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Optional: power-supply interruption resilience (separate resilience check, not flooding)</t>
+    </r>
+  </si>
+  <si>
+    <t>Network DoS / Flood Testing;
+Protocol Fuzzing (fieldbus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scapy (PROFINET/PROFIsafe flood generation) 
++ boofuzz (protocol fuzzing of the fieldbus interface). </t>
+  </si>
+  <si>
+    <t>Explicitly tests for the absence of rate limiting on the fieldbus (CR 7.1 RE(1)), which generic web-DoS tools do not cover. Scapy generates high-rate/oversized PROFINET traffic to test flood resilience; 
+boofuzz sends malformed frames to test stack robustness (CR 3.5). Observe whether the device stays in Operate, passivates cleanly, or becomes unstable.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">B (Safety Config), 
+G (Operating Mode)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Communication Config (NameOfStation/IP-affected by DCP)</t>
+    </r>
+  </si>
+  <si>
+    <t>F-address change and FW-update mode entry require physical access to the rotary/DIL switches plus a power-cycle, a physical-presence barrier for these two specific actions. 
+IoT-Core is designed read-only (no parameter writes via IoT). 
+Parameter writes occur only via the fieldbus/PLC engineering tool.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Major finding: device-side password protection for safety-parameter writes was explicitly dropped; 
+IoT-Core was made read-only instead. 
+(a) Parameter writes via fieldbus: authorization is fully delegated to an external, unverified assumption (locked cabinet, restricted network); 
+CR 1.1/1.2/2.1 are not enforced on the device itself. No mechanism exists for learning-phase settings. 
+(b) DCP "Reset to Factory" operates at Layer 2 and is, per general PROFINET knowledge, unauthenticated,  a node in the same segment could reset safety-relevant/communication config (Mode 2, optionally 3/4) without touching the physical switch barrier. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NOTE: SRIO-7772/3030 describe only the reset modes, not their authentication → this is based on general protocol knowledge and MUST be verified by test, not treated as established fact</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. 
+(c) IoT-Core write path: expected to be correctly blocked (read-only): tested for confirmation, not to prove the gap. 
+(d) Physical barrier robustness: whether the switch position can be changed without visible tampering.</t>
+    </r>
+  </si>
+  <si>
+    <t>Network:  PROFINET acyclic parameter records (param-begin/write/param-end);
+Network: DCP (Layer 2, factory reset);
+Web/API: IoT-Core HTTP (write attempt, negative); 
+Physical:  rotary/DIL switch (separate bench)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (a) Scapy (custom PROFINET param-begin/write/param-end sequence per SRIO-7749, sent WITHOUT prior physical switch access). 
+(b) pnio_dcp / profi-dcp (Python) or Scapy (scapy.contrib.pnio_dcp) for the factory-reset request + Wireshark ("Set OK" response verification). 
+(c) curl / OWASP ZAP (unauthenticated PUT/POST against IoT-Core parametrization endpoints,  expected: blocked). 
+(d) manual physical bypass test (change switch without visible tampering) + FW-update-mode-entry replay (Wireshark reference capture of the legitimate trigger + Scapy replay without the physical switch). </t>
+  </si>
+  <si>
+    <t>Network auth/authz tests (fieldbus + DCP),  primary. 
+Physical F-address/mode test + power-cycle,  separate bench. 
+SEQUENCING: a power-cycle may already clear the error log (RQ-012),  run any log-dependent step BEFORE the power-cycle.</t>
+  </si>
+  <si>
+    <t>Flood / fuzzing test (dedicated controlled window; disruptive)</t>
+  </si>
+  <si>
+    <t>(a) Scapy directly proves the core gap: since authorization is fully delegated to the physical switch (asset G) and CR 1.1/1.2/2.1 are not device-enforced, test whether a pure network attacker , without switch access,  can send a valid param-begin/write/param-end sequence that the SCPU accepts. A positive finding (frame processed) confirms the physical barrier is the only effective control and is bypassable by protocol knowledge alone. 
+(b) pnio_dcp offers a high-level factory-reset request (DCPControlBlock) without manual frame building; Wireshark confirms via the "Set OK" response whether the reset executed,  same normative gap over the network path. 
+(c) curl/ZAP confirm the IoT-Core HTTP path has no write/auth gate; since IoT-Core is documented read-only, a negative result (no write possible) is expected,  this validates that path is secured, not the gap itself. 
+(d) The physical bypass test independently checks whether the switch position can be changed without visible damage, ruling out that the assumed physical barrier is trivially circumvented.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I (tracing log) 
+</t>
+  </si>
+  <si>
+    <t>Non-volatile circular-buffer error log (≥100 entries), readable via IoT-Core.
+Survives non-cold-start resets but is cleared on coldstart; 
+when full, oldest entries are overwritten (circular buffer).</t>
+  </si>
+  <si>
+    <t>Confirmed non-conformity , two independent conflicts with the 5-year retention mandate: 
+(1) Deletion: the log is explicitly cleared on every coldstart (SRIO-6521), so intervention data does not persist across a coldstart. 
+(2) Capacity: the log is a fixed ≥100-entry circular buffer (SRIO-10703/10663), so once full, older intervention data is overwritten regardless of the 5-year window. Neither mechanism provides the durable per-intervention retention RQ-012 requires.</t>
+  </si>
+  <si>
+    <t>Web/API:  IoT-Core HTTP (/devicestatus/errorlog, read); 
+Physical:  power cycle (coldstart trigger))</t>
+  </si>
+  <si>
+    <t>Data Persistence/ Retention Testing;
+Physical Interface Testing (Power Cycle)</t>
+  </si>
+  <si>
+    <t>curl (read /devicestatus/errorlog before/after coldstart; 
+and to fill/observe the circular buffer) + physical power-cycle.
+.</t>
+  </si>
+  <si>
+    <t>curl reads the log before and after the coldstart, enabling direct comparison of entry count and content. The physical power-cycle reliably triggers the documented coldstart-deletion mechanism. 
+A single run is sufficient as structural evidence , one deletion already contradicts the 5-year mandate; 
+a real 5-year test is neither practical nor necessary since the mechanism is documented as consistent/reproducible. 
+Separately, generating &gt;100 events demonstrates the circular-buffer overwrite (capacity conflict), without any power-cycle.</t>
+  </si>
+  <si>
+    <t>Forced coldstart: run LAST (destroys the log state for this unit). 
+SEQUENCING: perform all log-dependent tests (RQ-003/008/009/011) BEFORE this coldstart.</t>
+  </si>
+  <si>
+    <t>I (Audit Data); 
+D (Safety Sofware)</t>
+  </si>
+  <si>
+    <t>Current firmware version readable via IoT-Core (/deviceinfo/swrevision, /firmware/version) and PROFINET I&amp;M0/I&amp;M5; 
+manufacturer-hosted Release Notes document version history per release (SRIO-16242).</t>
+  </si>
+  <si>
+    <t>The device exposes only the CURRENT firmware version, not a historical, per-device, per-upload log. 
+Release Notes are a manufacturer/website artifact, not device-resident, not per-device/serial, not tamper-evident, with no guaranteed 5-year retention per upload and no timestamp per upload, so they do not satisfy the literal requirement. prEN 50742 §7.3.1 explicitly excludes SW-version storage from the tracing log, reinforcing the gap. 
+Missing properties vs. requirement: device-residence, tamper-evidence, per-upload record, per-upload timestamp, 5-year retention.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Web/API:  IoT-Core HTTP (/deviceinfo/swrevision, /firmware/version); 
+Network: PROFINET I&amp;M0/I&amp;M5 (software revision/annotation);
+Documentation: manufacturer Release Notes (review artifact)</t>
+  </si>
+  <si>
+    <t>Version Read-out (device);
+Documentation Review (structural / negative proof)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">curl (query the firmware-version endpoints,  confirms only current version exposed) +
+manual document review (Release Notes vs. the literal RQ-013 properties). 
+Optional: Wireshark for I&amp;M5 cross-check. </t>
+  </si>
+  <si>
+    <t>Curl confirms the IoT-Core API returns only the currently installed firmware version, not a historical sequence of previous uploads,  supporting evidence that no device-resident version-tracking mechanism exists. 
+The actual proof is the documentation review: Release Notes are external, not tied to device/serial, with no guaranteed 5-year per-upload retention and no tamper protection, so they do not meet the tamper-evident, device-resident tracing-log requirement. 
+This is a structural (missing-feature) finding verifiable without active testing, analogous to the SVV-1 negative confirmation used at RQ-005.</t>
+  </si>
+  <si>
+    <t>Documentation review (structural finding; no active test)</t>
   </si>
 </sst>
 </file>
@@ -1195,13 +1255,6 @@
       <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1260,6 +1313,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1335,19 +1395,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" textRotation="180"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1613,10 +1673,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1956,29 +2012,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB352A9E-FA09-4936-805B-24B06A598CDB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:P68"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.453125" style="1"/>
-    <col min="3" max="3" width="15.26953125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.81640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="68.26953125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="68.453125" style="1" customWidth="1"/>
-    <col min="8" max="9" width="35.54296875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="37.81640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="74.7265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="51.54296875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="42.26953125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="56.453125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="23.7265625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="11.42578125" style="1"/>
+    <col min="3" max="3" width="15.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="68.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="68.42578125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="35.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="37.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="74.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="51.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="42.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="56.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" style="1" customWidth="1"/>
     <col min="16" max="16" width="22" style="1" customWidth="1"/>
-    <col min="17" max="17" width="33.7265625" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="11.453125" style="1"/>
+    <col min="17" max="17" width="33.7109375" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="2:16" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
@@ -2022,7 +2081,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="182.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:16" ht="182.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
@@ -2069,7 +2128,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="165" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:16" ht="165" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>28</v>
       </c>
@@ -2113,7 +2172,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="2:16" ht="197.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:16" ht="197.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="10" t="s">
         <v>41</v>
       </c>
@@ -2157,7 +2216,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="145.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:16" ht="145.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="10" t="s">
         <v>54</v>
       </c>
@@ -2201,7 +2260,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="235.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:16" ht="235.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="13" t="s">
         <v>67</v>
       </c>
@@ -2245,7 +2304,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="178.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:16" ht="178.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="11" t="s">
         <v>79</v>
       </c>
@@ -2289,7 +2348,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="2:16" ht="175.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" ht="175.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="11" t="s">
         <v>92</v>
       </c>
@@ -2333,7 +2392,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="164.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" ht="164.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>104</v>
       </c>
@@ -2368,7 +2427,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="132" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" ht="180" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
         <v>114</v>
       </c>
@@ -2382,223 +2441,223 @@
         <v>44</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="E13" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" ht="408.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="F14" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="13" spans="2:16" ht="173.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="11" t="s">
+      <c r="J14" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="177" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="2:16" ht="408.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16" ht="162" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>147</v>
+        <v>227</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>148</v>
+        <v>228</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>149</v>
+        <v>229</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>151</v>
+        <v>231</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>153</v>
+        <v>233</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16" ht="189.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" ht="189.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="12" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>156</v>
+        <v>235</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>157</v>
+        <v>236</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>158</v>
+        <v>237</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>159</v>
+        <v>238</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>160</v>
+        <v>239</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>161</v>
+        <v>240</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>162</v>
+        <v>241</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" ht="192" customHeight="1" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="192" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="12" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>241</v>
+        <v>204</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>237</v>
+        <v>200</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>236</v>
+        <v>199</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="252" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:12" ht="249" x14ac:dyDescent="0.25">
       <c r="E19" s="8" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="66" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="67" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="68" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="66" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="22" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 INTERNAL</oddFooter>
   </headerFooter>
@@ -2611,438 +2670,438 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D436C63D-BC80-4342-876E-1B6D43B6666C}">
   <dimension ref="A1:J50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>193</v>
+        <v>156</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>194</v>
+        <v>157</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>196</v>
+        <v>159</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1" t="s">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>207</v>
+        <v>170</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>208</v>
+        <v>171</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
-        <v>213</v>
+        <v>176</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>216</v>
+        <v>179</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>217</v>
+        <v>180</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="B39" s="2"/>
       <c r="J39" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="4"/>
       <c r="J40" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>227</v>
+        <v>190</v>
       </c>
       <c r="B41" s="4"/>
     </row>
-    <row r="42" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="4"/>
     </row>
-    <row r="43" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="B43" s="4"/>
     </row>
-    <row r="44" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="B44" s="2"/>
     </row>
-    <row r="45" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="B45" s="2"/>
     </row>
-    <row r="46" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="130.5" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="150" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="B48" s="2"/>
     </row>
-    <row r="49" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="B49" s="2"/>
     </row>
-    <row r="50" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>232</v>
+        <v>195</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/Asset-Mapping.xlsx
+++ b/Asset-Mapping.xlsx
@@ -1673,6 +1673,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Asset-Mapping.xlsx
+++ b/Asset-Mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifmworld-my.sharepoint.com/personal/nathalie_nuber_ifm_com/Documents/Documents/DHBW/Bachelorarbeit/Bachelorarbeit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{67C771C2-39B1-4E7D-ABF9-CEC1F090999D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{921E1CD0-001A-4765-9DF2-10B9A9D077B1}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="8_{67C771C2-39B1-4E7D-ABF9-CEC1F090999D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{114D74D4-A427-446F-9918-F43FB3A12522}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A49BA81-CDEC-4679-BB9D-EFEA5E788525}"/>
+    <workbookView xWindow="10690" yWindow="6390" windowWidth="19420" windowHeight="11500" xr2:uid="{4A49BA81-CDEC-4679-BB9D-EFEA5E788525}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="244">
   <si>
     <t>MVO-ID</t>
   </si>
@@ -1207,6 +1207,9 @@
   </si>
   <si>
     <t>Documentation review (structural finding; no active test)</t>
+  </si>
+  <si>
+    <t>Gegenmaßnahmen können NIST SP 800-92,</t>
   </si>
 </sst>
 </file>
@@ -2605,6 +2608,9 @@
       <c r="L16" s="2" t="s">
         <v>242</v>
       </c>
+      <c r="M16" s="1" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="17" spans="2:12" ht="192" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="12" t="s">
